--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +519,7 @@
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="48" customWidth="1" min="5" max="5"/>
+    <col width="53" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1656,27 +1692,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>SEMANAL - 24 E 28/09/25</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>SEMANAL - 24 E 28/09/25</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>#03 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
-      <c r="C50" s="3" t="n">
-        <v>123796</v>
-      </c>
-      <c r="D50" s="4" t="inlineStr">
-        <is>
-          <t>DESINFETANTE START VOREL 2L LAVANDA</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="n">
-        <v>13.5</v>
+      <c r="C50" s="8" t="n">
+        <v>123791</v>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2L</t>
+        </is>
+      </c>
+      <c r="E50" s="9" t="inlineStr">
+        <is>
+          <t>CITRUS, EUCALIPTO, FLORAL, JASMIM, LAVANDA, PINHO</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="51">

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +35,24 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -59,7 +77,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,24 +115,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -476,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -538,9 +574,9 @@
           <t>ARROZ BRILHANTE PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr"/>
-      <c r="F2" s="6" t="n">
-        <v>23.4</v>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="5" t="n">
+        <v>23.99</v>
       </c>
     </row>
     <row r="3">
@@ -562,9 +598,9 @@
           <t>ARROZ FLORA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="6" t="n">
-        <v>19.8</v>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="5" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="4">
@@ -586,9 +622,9 @@
           <t>ARROZ PIANTA PCT 5KG TIPO 1 BRANCO</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="n">
-        <v>16.2</v>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="5" t="n">
+        <v>14.99</v>
       </c>
     </row>
     <row r="5">
@@ -610,9 +646,9 @@
           <t xml:space="preserve">FEIJÃO PRETO PEROLA 1KG PREMIUM </t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="n">
-        <v>7.38</v>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="5" t="n">
+        <v>5.39</v>
       </c>
     </row>
     <row r="6">
@@ -634,9 +670,9 @@
           <t>AÇUCAR CRISTAL ITAJA 2KG</t>
         </is>
       </c>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="n">
-        <v>7.2</v>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="5" t="n">
+        <v>7.49</v>
       </c>
     </row>
     <row r="7">
@@ -658,32 +694,32 @@
           <t>FEIJÃO CARIOCA KALDINHO 1KG</t>
         </is>
       </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="n">
-        <v>5.76</v>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="5" t="n">
+        <v>5.69</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>#01 MERCEARIA - #02 ÓLEOS E GORDURAS</t>
         </is>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="C8" s="7" t="n">
         <v>106680</v>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>ÓLEO DE SOJA SOYA 900ML</t>
         </is>
       </c>
-      <c r="E8" s="5" t="inlineStr"/>
-      <c r="F8" s="6" t="n">
+      <c r="E8" s="9" t="inlineStr"/>
+      <c r="F8" s="10" t="n">
         <v>9</v>
       </c>
     </row>
@@ -714,32 +750,32 @@
           <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
         </is>
       </c>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="n">
-        <v>19.8</v>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="5" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
         </is>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="7" t="n">
         <v>101136</v>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t>CAFÉ PILÃO 250G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="n">
+      <c r="E11" s="9" t="inlineStr"/>
+      <c r="F11" s="10" t="n">
         <v>18</v>
       </c>
     </row>
@@ -762,9 +798,9 @@
           <t>CAFÉ SANTA CLARA 250G CLASSICO</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="n">
-        <v>17.1</v>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="5" t="n">
+        <v>16.99</v>
       </c>
     </row>
     <row r="13">
@@ -786,9 +822,9 @@
           <t>BISCOITO CREAM CRACKER FORTALEZA 350G</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="n">
-        <v>7.2</v>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="5" t="n">
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
@@ -810,9 +846,9 @@
           <t>BISCOITO ROSQUINHA SULLPER 600G COCO</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="n">
-        <v>8.1</v>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="5" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="15">
@@ -834,9 +870,9 @@
           <t>AZEITE DE OLIVA SINHA 500ML EXTRA VIRGEM</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="n">
-        <v>58.95</v>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="5" t="n">
+        <v>57.99</v>
       </c>
     </row>
     <row r="16">
@@ -858,13 +894,13 @@
           <t>CATCHUP OLÉ 400G</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>PICANTE, TRADICIONAL</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n">
-        <v>7.2</v>
+      <c r="F16" s="5" t="n">
+        <v>6.99</v>
       </c>
     </row>
     <row r="17">
@@ -886,9 +922,9 @@
           <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
         </is>
       </c>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="n">
-        <v>8.640000000000001</v>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="5" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="18">
@@ -910,9 +946,9 @@
           <t>EXTRATO DE TOMATE QUERO LATA 350G</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="n">
-        <v>8.1</v>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="5" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="19">
@@ -934,9 +970,9 @@
           <t>EXTRATO DE TOMATE SOFRUTA SACHÊ 140G</t>
         </is>
       </c>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="n">
-        <v>2.61</v>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="5" t="n">
+        <v>1.79</v>
       </c>
     </row>
     <row r="20">
@@ -958,9 +994,9 @@
           <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="n">
-        <v>16.2</v>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="5" t="n">
+        <v>14.99</v>
       </c>
     </row>
     <row r="21">
@@ -982,32 +1018,32 @@
           <t>MOLHO QUERO PRONTO SACHÊ 240G TRADICIONAL</t>
         </is>
       </c>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="n">
-        <v>2.7</v>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="5" t="n">
+        <v>2.19</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
         </is>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="C22" s="7" t="n">
         <v>266057</v>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>PIMENTA LINKEN 2KG BIQUINHO VERMELHA</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="n">
+      <c r="E22" s="9" t="inlineStr"/>
+      <c r="F22" s="10" t="n">
         <v>135</v>
       </c>
     </row>
@@ -1030,9 +1066,9 @@
           <t>TEMPERO COMPLETO ARISCO 1KG COM PIMENTA</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="n">
-        <v>15.3</v>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="5" t="n">
+        <v>14.49</v>
       </c>
     </row>
     <row r="24">
@@ -1054,13 +1090,13 @@
           <t>VINAGRE CASTELO 750ML</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>ALCOOL, ALCOOL COLORIDO</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n">
-        <v>4.41</v>
+      <c r="F24" s="5" t="n">
+        <v>4.19</v>
       </c>
     </row>
     <row r="25">
@@ -1082,9 +1118,9 @@
           <t>MILHO VERDE QUERO LATA 170G</t>
         </is>
       </c>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="n">
-        <v>4.68</v>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="5" t="n">
+        <v>4.09</v>
       </c>
     </row>
     <row r="26">
@@ -1106,9 +1142,9 @@
           <t>PALMITO PERIQUITU 300G AÇAI RODELA TEMPERADO</t>
         </is>
       </c>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="n">
-        <v>20.7</v>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="5" t="n">
+        <v>19.99</v>
       </c>
     </row>
     <row r="27">
@@ -1130,13 +1166,13 @@
           <t>SARDINHA GOMES DA COSTA 125G</t>
         </is>
       </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>TOMATE, ÓLEO</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n">
-        <v>6.3</v>
+      <c r="F27" s="5" t="n">
+        <v>5.99</v>
       </c>
     </row>
     <row r="28">
@@ -1158,9 +1194,9 @@
           <t>CUSCUZ DE MILHO SINHA 500G</t>
         </is>
       </c>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="n">
-        <v>3.24</v>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="5" t="n">
+        <v>2.79</v>
       </c>
     </row>
     <row r="29">
@@ -1182,9 +1218,9 @@
           <t>FARINHA DE MANDIOCA JOÃOZINHO 1KG BRANCA GROSSA</t>
         </is>
       </c>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="n">
-        <v>8.1</v>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="5" t="n">
+        <v>8.19</v>
       </c>
     </row>
     <row r="30">
@@ -1206,9 +1242,9 @@
           <t>FARINHA DE TRIGO DONA BENTA 1KG SEM FERMENTO</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="n">
-        <v>5.85</v>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="5" t="n">
+        <v>5.79</v>
       </c>
     </row>
     <row r="31">
@@ -1230,9 +1266,9 @@
           <t>FARINHA DE TRIGO MIRELLA PAPEL 1KG COM FERMENTO</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="n">
-        <v>5.31</v>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="5" t="n">
+        <v>5.29</v>
       </c>
     </row>
     <row r="32">
@@ -1254,9 +1290,9 @@
           <t>FLOCÃO DE ARROZ BONOARROZ 500G</t>
         </is>
       </c>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="n">
-        <v>3.06</v>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="5" t="n">
+        <v>2.89</v>
       </c>
     </row>
     <row r="33">
@@ -1278,9 +1314,9 @@
           <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="n">
-        <v>3.96</v>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="5" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="34">
@@ -1302,9 +1338,9 @@
           <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="n">
-        <v>9</v>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="5" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="35">
@@ -1326,9 +1362,9 @@
           <t>POLVILHO NANA E CIA 1KG DOCE</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="6" t="n">
-        <v>9.9</v>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="5" t="n">
+        <v>8.99</v>
       </c>
     </row>
     <row r="36">
@@ -1350,9 +1386,9 @@
           <t xml:space="preserve">BEBIDA LACTEA PIRAKIDS 200ML CHOCOLATE </t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="n">
-        <v>1.98</v>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="5" t="n">
+        <v>1.89</v>
       </c>
     </row>
     <row r="37">
@@ -1374,32 +1410,32 @@
           <t>CREME DE LEITE PIRACANJUBA 200G</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr"/>
-      <c r="F37" s="6" t="n">
-        <v>4.05</v>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="5" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
         </is>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="C38" s="7" t="n">
         <v>101083</v>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
         </is>
       </c>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="n">
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="10" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -1422,32 +1458,32 @@
           <t>LEITE LEITBOM 1L INTEGRAL</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="n">
-        <v>8.279999999999999</v>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="5" t="n">
+        <v>8.19</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
         </is>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="C40" s="7" t="n">
         <v>108252</v>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>LEITE PIRACANJUBA 1L EDGE DESNATADO</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="n">
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="10" t="n">
         <v>7.2</v>
       </c>
     </row>
@@ -1470,9 +1506,9 @@
           <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="n">
-        <v>43.2</v>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="5" t="n">
+        <v>42.99</v>
       </c>
     </row>
     <row r="42">
@@ -1494,9 +1530,9 @@
           <t>MACARRÃO GALO 500G ESPAGUETE VERMELHO Nº8</t>
         </is>
       </c>
-      <c r="E42" s="5" t="inlineStr"/>
-      <c r="F42" s="6" t="n">
-        <v>3.6</v>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="5" t="n">
+        <v>3.49</v>
       </c>
     </row>
     <row r="43">
@@ -1518,42 +1554,42 @@
           <t>MACARRÃO GALO 500G PENA AZUL</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="6" t="n">
-        <v>5.58</v>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="5" t="n">
+        <v>4.99</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>#02 MERCEARIA - MASSAS</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="n">
-        <v>152729</v>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">MACARRÃO SAFRA 500G ESPAGUETE SEMOLA </t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>#03 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
+        </is>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>100426</v>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>AGUA SANITÁRIA QBOA 1L</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="5" t="n">
+        <v>3.79</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1567,16 +1603,16 @@
         </is>
       </c>
       <c r="C46" s="3" t="n">
-        <v>100426</v>
+        <v>107943</v>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>AGUA SANITÁRIA QBOA 1L</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="n">
-        <v>3.96</v>
+          <t>AGUA SANITÁRIA YPÊ 2L</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="5" t="n">
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -1587,20 +1623,20 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
+          <t>#03 LIMPEZA - AMACIANTES</t>
         </is>
       </c>
       <c r="C47" s="3" t="n">
-        <v>107943</v>
+        <v>116139</v>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>AGUA SANITÁRIA YPÊ 2L</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="n">
-        <v>9</v>
+          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="5" t="n">
+        <v>7.69</v>
       </c>
     </row>
     <row r="48">
@@ -1615,16 +1651,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>116139</v>
+        <v>287170</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS +FAMILIA 2L FLORISTA</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="n">
-        <v>8.1</v>
+          <t>AMACIANTE DE ROUPAS MON BIJOU 1,7L + FRESCOR</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="5" t="n">
+        <v>11.49</v>
       </c>
     </row>
     <row r="49">
@@ -1639,16 +1675,16 @@
         </is>
       </c>
       <c r="C49" s="3" t="n">
-        <v>287170</v>
+        <v>270215</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE DE ROUPAS MON BIJOU 1,7L + FRESCOR</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="n">
-        <v>12.6</v>
+          <t>AMACIANTE DOWNY 500ML CONCENTRADO BRISA DE VERÃO</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="5" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="50">
@@ -1659,20 +1695,24 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - AMACIANTES</t>
+          <t>#03 LIMPEZA - DESINFETANTES</t>
         </is>
       </c>
       <c r="C50" s="3" t="n">
-        <v>270215</v>
+        <v>100279</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>AMACIANTE DOWNY 500ML CONCENTRADO BRISA DE VERÃO</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="n">
-        <v>13.5</v>
+          <t>DESINFETANTE PINHO BRIL 1L</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>BRISA MAR, CAMPOS DE LAVANDA, FLORES DE LIMÃO, PLUS</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>11.99</v>
       </c>
     </row>
     <row r="51">
@@ -1683,20 +1723,20 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - DESINFETANTES</t>
+          <t>#03 LIMPEZA - DETERGENTES</t>
         </is>
       </c>
       <c r="C51" s="3" t="n">
-        <v>100279</v>
+        <v>204526</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>DESINFETANTE PINHO BRIL 1L BRISA MAR</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="n">
-        <v>13.5</v>
+          <t>DESENGORDURANTE POLITRIZ 500ML</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="5" t="n">
+        <v>4.99</v>
       </c>
     </row>
     <row r="52">
@@ -1711,16 +1751,20 @@
         </is>
       </c>
       <c r="C52" s="3" t="n">
-        <v>204526</v>
+        <v>100423</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>DESENGORDURANTE POLITRIZ 500ML</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="n">
-        <v>5.85</v>
+          <t>DETERGENTE LIQUIDO LIMPOL 500ML</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>COCO, CRISTAL, JABOTICABA, LAVANDA, LIMÃO, MAÇÃ, NEUTRO</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>2.69</v>
       </c>
     </row>
     <row r="53">
@@ -1731,24 +1775,24 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - DETERGENTES</t>
+          <t>#03 LIMPEZA - LIMPA ALUMINIO</t>
         </is>
       </c>
       <c r="C53" s="3" t="n">
-        <v>100423</v>
+        <v>118939</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO LIMPOL 500ML</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>COCO, CRISTAL, JABOTICABA, LAVANDA, LIMÃO, MAÇÃ, NEUTRO</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="n">
-        <v>2.88</v>
+          <t>LIMPA ALUMINIO POLYLAR 500ML</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>LIMÃO, MAÇÃ</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
@@ -1759,24 +1803,20 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - LIMPA ALUMINIO</t>
+          <t>#03 LIMPEZA - SABÃO</t>
         </is>
       </c>
       <c r="C54" s="3" t="n">
-        <v>118939</v>
+        <v>257710</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>LIMPA ALUMINIO POLYLAR 500ML</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>LIMÃO, MAÇÃ</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>5.4</v>
+          <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="5" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="55">
@@ -1791,16 +1831,16 @@
         </is>
       </c>
       <c r="C55" s="3" t="n">
-        <v>257710</v>
+        <v>210874</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="n">
-        <v>14.4</v>
+          <t xml:space="preserve">SABÃO EM PÓ OMO 400G LAVAGEM PERFEITA </t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="5" t="n">
+        <v>8.99</v>
       </c>
     </row>
     <row r="56">
@@ -1815,16 +1855,20 @@
         </is>
       </c>
       <c r="C56" s="3" t="n">
-        <v>210874</v>
+        <v>286199</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">SABÃO EM PÓ OMO 400G LAVAGEM PERFEITA </t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="6" t="n">
-        <v>9.9</v>
+          <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>MACIEZ, PRIMAVERA</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>10.99</v>
       </c>
     </row>
     <row r="57">
@@ -1835,57 +1879,53 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>#03 LIMPEZA - SABÃO</t>
+          <t>#03 LIMPEZA - SODAS</t>
         </is>
       </c>
       <c r="C57" s="3" t="n">
-        <v>286199</v>
+        <v>100373</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 800G</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>MACIEZ, PRIMAVERA</t>
-        </is>
-      </c>
-      <c r="F57" s="6" t="n">
-        <v>11.7</v>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="5" t="n">
+        <v>25.99</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>#03 LIMPEZA - SODAS</t>
-        </is>
-      </c>
-      <c r="C58" s="3" t="n">
-        <v>100373</v>
-      </c>
-      <c r="D58" s="4" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="6" t="n">
-        <v>25.2</v>
-      </c>
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+        </is>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>108686</v>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE ANTARCTICA 2L SODA LIMONADA</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="5" t="n">
+        <v>7.49</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -1899,40 +1939,40 @@
         </is>
       </c>
       <c r="C60" s="3" t="n">
-        <v>108686</v>
+        <v>104403</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE ANTARCTICA 2L SODA LIMONADA</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="6" t="n">
-        <v>7.56</v>
+          <t>REFRIGERANTE FANTA 2L UVA</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="5" t="n">
+        <v>9.49</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
-        </is>
-      </c>
-      <c r="C61" s="3" t="n">
-        <v>104406</v>
-      </c>
-      <c r="D61" s="4" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="n">
-        <v>10.35</v>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>156763</v>
+      </c>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 1L PROMOCIONAL</t>
+        </is>
+      </c>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="n">
+        <v>12.6</v>
       </c>
     </row>
     <row r="62">
@@ -1943,44 +1983,44 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
+          <t>#05 BEBIDA - CERVEJAS</t>
         </is>
       </c>
       <c r="C62" s="3" t="n">
-        <v>104403</v>
+        <v>242930</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>REFRIGERANTE FANTA 2L UVA</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="6" t="n">
-        <v>9.449999999999999</v>
+          <t>CERVEJA HEINEKEN 330ML</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr"/>
+      <c r="F62" s="5" t="n">
+        <v>6.89</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="n">
-        <v>156763</v>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>ENERGETICO EXTRA POWER 1L PROMOCIONAL</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="n">
-        <v>12.6</v>
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="inlineStr">
+        <is>
+          <t>#05 BEBIDA - CERVEJAS</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>157496</v>
+      </c>
+      <c r="D63" s="8" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
+        </is>
+      </c>
+      <c r="E63" s="9" t="inlineStr"/>
+      <c r="F63" s="10" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="64">
@@ -1991,20 +2031,20 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS</t>
+          <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>242930</v>
+        <v>298701</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="n">
-        <v>6.93</v>
+          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr"/>
+      <c r="F64" s="5" t="n">
+        <v>3.69</v>
       </c>
     </row>
     <row r="65">
@@ -2015,20 +2055,20 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS</t>
+          <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
       <c r="C65" s="3" t="n">
-        <v>157496</v>
+        <v>324556</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="n">
-        <v>13.5</v>
+          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="5" t="n">
+        <v>2.95</v>
       </c>
     </row>
     <row r="66">
@@ -2039,20 +2079,20 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C66" s="3" t="n">
-        <v>298701</v>
+        <v>102085</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 12 X 350ML LAGER SLEEK</t>
-        </is>
-      </c>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="6" t="n">
-        <v>3.78</v>
+          <t>CACHAÇA 51 965ML</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr"/>
+      <c r="F66" s="5" t="n">
+        <v>12.99</v>
       </c>
     </row>
     <row r="67">
@@ -2063,20 +2103,20 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>#05 BEBIDA - CERVEJAS CX</t>
+          <t>#05 BEBIDA - DESTILADOS</t>
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>324556</v>
+        <v>215568</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">CERVEJA SKOL 15 X 269ML PILSEN </t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="n">
-        <v>2.88</v>
+          <t>CACHAÇA BANANAZINHA 900ML</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr"/>
+      <c r="F67" s="5" t="n">
+        <v>38.99</v>
       </c>
     </row>
     <row r="68">
@@ -2091,64 +2131,16 @@
         </is>
       </c>
       <c r="C68" s="3" t="n">
-        <v>102085</v>
+        <v>102077</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>CACHAÇA 51 965ML</t>
-        </is>
-      </c>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="6" t="n">
-        <v>13.5</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="n">
-        <v>215568</v>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>CACHAÇA BANANAZINHA 900ML</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr"/>
-      <c r="F69" s="6" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>QUARTA/DOMINGO - 22 A 26/10/25</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>#05 BEBIDA - DESTILADOS</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="n">
-        <v>102077</v>
-      </c>
-      <c r="D70" s="4" t="inlineStr">
-        <is>
           <t>WHISKY OLD PARR 1L 12 ANOS</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="6" t="n">
-        <v>189</v>
+      <c r="E68" s="4" t="inlineStr"/>
+      <c r="F68" s="5" t="n">
+        <v>185.99</v>
       </c>
     </row>
   </sheetData>

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ PCT 5KG TIPO 1 BRANCO</t>
+          <t>ARROZ SEU ARROZ PCT 1KG TIPO 1 BRANCO</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr"/>

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="R$ #,##0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -58,8 +58,26 @@
       <color rgb="00000000"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +88,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0045A045"/>
+        <bgColor rgb="0045A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -91,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -109,6 +133,18 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1876,51 +1912,51 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>QUINTA/DOMINGO - OFERTAS 08 A 11/01/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>QUINTA/DOMINGO - OFERTAS 08 A 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C60" s="3" t="n">
+      <c r="C60" s="8" t="n">
         <v>239446</v>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA AMSTEL LAGER 12 X 269ML </t>
         </is>
       </c>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="6" t="n">
-        <v>3.09</v>
+      <c r="E60" s="9" t="inlineStr"/>
+      <c r="F60" s="10" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>QUINTA/DOMINGO - OFERTAS 08 A 11/01/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>QUINTA/DOMINGO - OFERTAS 08 A 11/01/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>#05 BEBIDA - CERVEJAS CX</t>
         </is>
       </c>
-      <c r="C61" s="3" t="n">
+      <c r="C61" s="8" t="n">
         <v>170451</v>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">CERVEJA BRAHMA CHOPP 15 X 269ML </t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="n">
-        <v>3.09</v>
+      <c r="E61" s="9" t="inlineStr"/>
+      <c r="F61" s="10" t="n">
+        <v>2.99</v>
       </c>
     </row>
     <row r="62">

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6424740F-3D4B-46A6-864F-C18864CE2C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682AC0CB-0A21-4D2C-8001-7DDDD98A8127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -379,7 +376,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -399,21 +396,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -457,7 +464,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -465,22 +472,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -787,1326 +804,1326 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F76"/>
-  <sheetFormatPr defaultRowHeight="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="33.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="74.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.7109375" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>288949</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>100031</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="7">
         <v>22.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>199440</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>298239</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="7">
         <v>6.59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>200178</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="7">
         <v>6.39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>106680</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="11"/>
       <c r="F7" s="7">
         <v>8.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>174725</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="7">
         <v>34.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>318330</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="11"/>
       <c r="F10" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>101137</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>114037</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>250013</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="7">
         <v>5.19</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>236062</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>321679</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="7">
         <v>7.39</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>318863</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="7">
         <v>8.39</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>239682</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>111378</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>312579</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>273714</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="11"/>
       <c r="F20" s="7">
         <v>7.49</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>100780</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="11"/>
       <c r="F21" s="7">
         <v>3.59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>111517</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="7">
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>188242</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="11"/>
       <c r="F23" s="7">
         <v>8.19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>115724</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>244444</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="11"/>
       <c r="F25" s="7">
         <v>1.79</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>100876</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="7">
         <v>14.49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>119560</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="11"/>
       <c r="F27" s="7">
         <v>5.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>106961</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="11" t="s">
         <v>42</v>
       </c>
       <c r="F28" s="7">
         <v>3.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>134749</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="11"/>
       <c r="F29" s="7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>100754</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="11"/>
       <c r="F30" s="7">
         <v>23.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>100705</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="E31" s="11" t="s">
         <v>48</v>
       </c>
       <c r="F31" s="7">
         <v>6.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>110330</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="11"/>
       <c r="F32" s="7">
         <v>1.89</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>100024</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="11"/>
       <c r="F33" s="7">
         <v>5.49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>100027</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="11"/>
       <c r="F34" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>100119</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="11"/>
       <c r="F35" s="7">
         <v>2.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>313828</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="11"/>
       <c r="F36" s="7">
         <v>3.69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>101130</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="11"/>
       <c r="F37" s="7">
         <v>7.49</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>145874</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="11"/>
       <c r="F38" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>133678</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="11"/>
       <c r="F39" s="7">
         <v>3.49</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>108434</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="11"/>
       <c r="F40" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>142446</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="11"/>
       <c r="F41" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>108252</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="11"/>
       <c r="F42" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>106922</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="11"/>
       <c r="F43" s="7">
         <v>39.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>131884</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="11"/>
       <c r="F44" s="7">
         <v>3.39</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>246970</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="11"/>
       <c r="F45" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>328759</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="11"/>
       <c r="F46" s="7">
         <v>3.39</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>126425</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="11"/>
       <c r="F47" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>100431</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="11"/>
       <c r="F49" s="7">
         <v>7.39</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="5">
         <v>116139</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="11"/>
       <c r="F50" s="7">
         <v>7.49</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="5">
         <v>260657</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="11"/>
       <c r="F51" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="5">
         <v>259583</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="11"/>
       <c r="F52" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="5">
         <v>111567</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="11"/>
       <c r="F53" s="7">
         <v>2.59</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="5">
         <v>197496</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="11"/>
       <c r="F54" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="5">
         <v>261360</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="11"/>
       <c r="F55" s="7">
         <v>10.39</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="5">
         <v>326954</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="11"/>
       <c r="F56" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="5">
         <v>228234</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="11"/>
       <c r="F57" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="5">
         <v>286199</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="5" t="s">
+      <c r="E58" s="11" t="s">
         <v>86</v>
       </c>
       <c r="F58" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="5">
         <v>100373</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="11"/>
       <c r="F59" s="7">
         <v>25.49</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="5">
         <v>236651</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="11"/>
       <c r="F61" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="5">
         <v>104406</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="11"/>
       <c r="F63" s="7">
         <v>10.49</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="5">
         <v>104404</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="11"/>
       <c r="F64" s="7">
         <v>9.49</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="5">
         <v>104410</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="5">
         <v>102282</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="11"/>
       <c r="F66" s="7">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="5">
         <v>286325</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="11"/>
       <c r="F67" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="5">
         <v>102149</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="11"/>
       <c r="F68" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="5">
         <v>242930</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E69" s="5"/>
+      <c r="E69" s="11"/>
       <c r="F69" s="7">
         <v>6.89</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="5">
         <v>287369</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="5"/>
+      <c r="E70" s="11"/>
       <c r="F70" s="7">
         <f>15*3.79</f>
         <v>56.85</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="5">
         <v>170451</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E71" s="5"/>
+      <c r="E71" s="11"/>
       <c r="F71" s="7">
         <f>15*3.09</f>
         <v>46.349999999999994</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="5">
         <v>324556</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="E72" s="5"/>
+      <c r="E72" s="11"/>
       <c r="F72" s="7">
         <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="5">
         <v>102085</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E73" s="5"/>
+      <c r="E73" s="11"/>
       <c r="F73" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="5">
         <v>110373</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="E74" s="5"/>
+      <c r="E74" s="11"/>
       <c r="F74" s="7">
         <v>109.99</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="5">
         <v>102077</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E75" s="5"/>
+      <c r="E75" s="11"/>
       <c r="F75" s="7">
         <v>179.99</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="5">
         <v>295198</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E76" s="5"/>
+      <c r="E76" s="11"/>
       <c r="F76" s="7">
         <v>11.59</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="91" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{682AC0CB-0A21-4D2C-8001-7DDDD98A8127}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A2A37F-906B-4DCE-932A-C6329452A578}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -804,17 +804,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F76"/>
-  <sheetFormatPr defaultRowHeight="33.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.7109375" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="74.7109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="24.7109375" style="12" customWidth="1"/>
+    <col min="5" max="5" width="38.140625" style="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -834,7 +834,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -852,7 +852,7 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
@@ -870,7 +870,7 @@
         <v>22.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -888,7 +888,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -906,7 +906,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -924,7 +924,7 @@
         <v>6.39</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -942,7 +942,7 @@
         <v>8.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -960,7 +960,7 @@
         <v>34.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -978,7 +978,7 @@
         <v>13.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
@@ -996,7 +996,7 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
@@ -1014,7 +1014,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>8.39</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
@@ -1122,7 +1122,7 @@
         <v>15.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
@@ -1140,7 +1140,7 @@
         <v>13.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
@@ -1158,7 +1158,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>3.59</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
@@ -1212,7 +1212,7 @@
         <v>8.19</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
@@ -1248,7 +1248,7 @@
         <v>1.79</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>14.49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -1304,7 +1304,7 @@
         <v>3.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>4.59</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>23.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1360,7 @@
         <v>6.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>1.89</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
@@ -1396,7 +1396,7 @@
         <v>5.49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
@@ -1432,7 +1432,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>3.69</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
@@ -1468,7 +1468,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
@@ -1486,7 +1486,7 @@
         <v>10.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>3.49</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>6.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
@@ -1576,7 +1576,7 @@
         <v>39.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>3.19</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>7.39</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
@@ -1684,7 +1684,7 @@
         <v>7.49</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>10.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>4.99</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>10.39</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
@@ -1830,7 +1830,7 @@
         <v>10.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>25.49</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>10.49</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
@@ -1902,7 +1902,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
@@ -1920,7 +1920,7 @@
         <v>7.99</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>5.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>6.89</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>56.85</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
@@ -2030,7 +2030,7 @@
         <v>46.349999999999994</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>6</v>
       </c>
@@ -2049,7 +2049,7 @@
         <v>43.35</v>
       </c>
     </row>
-    <row r="73" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>12.99</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
@@ -2085,7 +2085,7 @@
         <v>109.99</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
@@ -2103,7 +2103,7 @@
         <v>179.99</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,17 +10,12 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD2AE9D-FBFC-41FD-93CD-27756E8016A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD2AE9D-FBFC-41FD-93CD-27756E8016A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016FEC5A-AA4A-485C-8552-F21586CE6FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="116">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -172,6 +172,9 @@
     <t>MUCILON NESTLE 180G</t>
   </si>
   <si>
+    <t>ARROZ, ARROZ E AVEIA INTEGRAL, MILHO, MULTICEREAIS</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - LATICÍNIOS - BEBIDAS LACTEAS</t>
   </si>
   <si>
@@ -229,9 +232,6 @@
     <t>MACARRÃO INSTANTANEO NISSIN UFO 81G</t>
   </si>
   <si>
-    <t>MACARRÃO INSTANTANEO NISSIN UFO 93G GALINHA CAIPIRA</t>
-  </si>
-  <si>
     <t>MACARRÃO INSTANTANEO NISSIN UFO 96G CURRY</t>
   </si>
   <si>
@@ -307,6 +307,36 @@
     <t>SUCO NUTRI 1L</t>
   </si>
   <si>
+    <t>#05 BEBIDA - CERVEJAS</t>
+  </si>
+  <si>
+    <t>CERVEJA ANTARCTICA ORIGINAL LONG NECK 300ML</t>
+  </si>
+  <si>
+    <t>REBAIXA - HEINEKEN ATÉ 07/03/2026</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 269ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA HEINEKEN LAGER LONG NECK 250ML </t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - CERVEJAS CX</t>
+  </si>
+  <si>
+    <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CERVEJA ANTARCTICA ORIGINAL LONG NECK 12 X 300ML </t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 8 X 269ML</t>
+  </si>
+  <si>
+    <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
+  </si>
+  <si>
     <t>#05 BEBIDA - DESTILADOS</t>
   </si>
   <si>
@@ -335,6 +365,9 @@
   </si>
   <si>
     <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN LAGER LONG NECK 6 X 250ML</t>
   </si>
 </sst>
 </file>
@@ -344,7 +377,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -380,8 +413,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +443,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -422,7 +479,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -436,7 +493,13 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -446,6 +509,21 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,18 +826,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F73"/>
-  <sheetFormatPr defaultColWidth="41.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F80"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="51.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42" customWidth="1"/>
+    <col min="2" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="57" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="14" customWidth="1"/>
+    <col min="6" max="6" width="12" style="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -775,10 +850,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
@@ -795,8 +870,8 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="13"/>
+      <c r="F2" s="9">
         <v>15.99</v>
       </c>
     </row>
@@ -813,8 +888,8 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="13"/>
+      <c r="F3" s="9">
         <v>22.99</v>
       </c>
     </row>
@@ -831,8 +906,8 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="13"/>
+      <c r="F4" s="9">
         <v>15.99</v>
       </c>
     </row>
@@ -849,8 +924,8 @@
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="13"/>
+      <c r="F5" s="9">
         <v>6.49</v>
       </c>
     </row>
@@ -867,8 +942,8 @@
       <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="13"/>
+      <c r="F6" s="9">
         <v>8.19</v>
       </c>
     </row>
@@ -885,8 +960,8 @@
       <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="13"/>
+      <c r="F7" s="9">
         <v>21.99</v>
       </c>
     </row>
@@ -903,8 +978,8 @@
       <c r="D9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="13"/>
+      <c r="F9" s="9">
         <v>12.99</v>
       </c>
     </row>
@@ -921,8 +996,8 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
+      <c r="E10" s="13"/>
+      <c r="F10" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
@@ -939,8 +1014,8 @@
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="13"/>
+      <c r="F11" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
@@ -957,8 +1032,8 @@
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="13"/>
+      <c r="F12" s="9">
         <v>5.19</v>
       </c>
     </row>
@@ -975,8 +1050,8 @@
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="13"/>
+      <c r="F13" s="9">
         <v>3.69</v>
       </c>
     </row>
@@ -993,8 +1068,8 @@
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="13"/>
+      <c r="F14" s="9">
         <v>7.39</v>
       </c>
     </row>
@@ -1011,8 +1086,8 @@
       <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
+      <c r="E15" s="13"/>
+      <c r="F15" s="9">
         <v>8.49</v>
       </c>
     </row>
@@ -1029,8 +1104,8 @@
       <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="13"/>
+      <c r="F16" s="9">
         <v>12.99</v>
       </c>
     </row>
@@ -1047,8 +1122,8 @@
       <c r="D17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="13"/>
+      <c r="F17" s="9">
         <v>26.99</v>
       </c>
     </row>
@@ -1065,8 +1140,8 @@
       <c r="D18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="13"/>
+      <c r="F18" s="9">
         <v>13.99</v>
       </c>
     </row>
@@ -1083,8 +1158,8 @@
       <c r="D19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="13"/>
+      <c r="F19" s="9">
         <v>8.99</v>
       </c>
     </row>
@@ -1101,8 +1176,8 @@
       <c r="D20" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="13"/>
+      <c r="F20" s="9">
         <v>7.59</v>
       </c>
     </row>
@@ -1119,8 +1194,8 @@
       <c r="D21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="13"/>
+      <c r="F21" s="9">
         <v>3.19</v>
       </c>
     </row>
@@ -1137,8 +1212,8 @@
       <c r="D22" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="13"/>
+      <c r="F22" s="9">
         <v>5.49</v>
       </c>
     </row>
@@ -1155,8 +1230,8 @@
       <c r="D23" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="13"/>
+      <c r="F23" s="9">
         <v>2.29</v>
       </c>
     </row>
@@ -1173,8 +1248,8 @@
       <c r="D24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="13"/>
+      <c r="F24" s="9">
         <v>13.99</v>
       </c>
     </row>
@@ -1191,8 +1266,8 @@
       <c r="D25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="13"/>
+      <c r="F25" s="9">
         <v>5.69</v>
       </c>
     </row>
@@ -1209,8 +1284,8 @@
       <c r="D26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="13"/>
+      <c r="F26" s="9">
         <v>3.79</v>
       </c>
     </row>
@@ -1227,8 +1302,8 @@
       <c r="D27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="13"/>
+      <c r="F27" s="9">
         <v>8.99</v>
       </c>
     </row>
@@ -1245,8 +1320,8 @@
       <c r="D28" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="13"/>
+      <c r="F28" s="9">
         <v>13.99</v>
       </c>
     </row>
@@ -1263,8 +1338,8 @@
       <c r="D29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="13"/>
+      <c r="F29" s="9">
         <v>5.69</v>
       </c>
     </row>
@@ -1281,8 +1356,8 @@
       <c r="D30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="13"/>
+      <c r="F30" s="9">
         <v>6.99</v>
       </c>
     </row>
@@ -1299,8 +1374,8 @@
       <c r="D31" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="13"/>
+      <c r="F31" s="9">
         <v>2.59</v>
       </c>
     </row>
@@ -1317,8 +1392,8 @@
       <c r="D32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="13"/>
+      <c r="F32" s="9">
         <v>6.99</v>
       </c>
     </row>
@@ -1335,8 +1410,10 @@
       <c r="D33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="9">
         <v>7.59</v>
       </c>
     </row>
@@ -1345,16 +1422,16 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3">
         <v>117680</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+        <v>52</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="9">
         <v>1.69</v>
       </c>
     </row>
@@ -1363,16 +1440,16 @@
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C35" s="3">
         <v>113183</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+        <v>54</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="9">
         <v>6.49</v>
       </c>
     </row>
@@ -1381,16 +1458,16 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C36" s="3">
         <v>101082</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+        <v>55</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="9">
         <v>5.39</v>
       </c>
     </row>
@@ -1399,16 +1476,16 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C37" s="3">
         <v>120230</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+        <v>57</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="9">
         <v>39.99</v>
       </c>
     </row>
@@ -1417,16 +1494,16 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C38" s="3">
         <v>228068</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+        <v>58</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="9">
         <v>6.59</v>
       </c>
     </row>
@@ -1435,16 +1512,16 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C39" s="3">
         <v>108252</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+        <v>59</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="9">
         <v>4.99</v>
       </c>
     </row>
@@ -1453,16 +1530,16 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C40" s="3">
         <v>142447</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+        <v>61</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="9">
         <v>15.99</v>
       </c>
     </row>
@@ -1471,16 +1548,16 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C41" s="3">
         <v>303196</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
+        <v>63</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="9">
         <v>3.49</v>
       </c>
     </row>
@@ -1489,16 +1566,16 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C42" s="3">
         <v>131884</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
+        <v>64</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="9">
         <v>3.19</v>
       </c>
     </row>
@@ -1507,16 +1584,16 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C43" s="3">
         <v>100642</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+        <v>65</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="9">
         <v>2.99</v>
       </c>
     </row>
@@ -1525,16 +1602,16 @@
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C44" s="3">
         <v>209415</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+        <v>66</v>
+      </c>
+      <c r="E44" s="13"/>
+      <c r="F44" s="9">
         <v>4.99</v>
       </c>
     </row>
@@ -1543,16 +1620,16 @@
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C45" s="3">
         <v>108460</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+        <v>68</v>
+      </c>
+      <c r="E45" s="13"/>
+      <c r="F45" s="9">
         <v>1.99</v>
       </c>
     </row>
@@ -1561,16 +1638,16 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C46" s="3">
         <v>267864</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+        <v>69</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="9">
         <v>6.69</v>
       </c>
     </row>
@@ -1579,35 +1656,35 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C47" s="3">
-        <v>314227</v>
+        <v>312904</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+        <v>70</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="9">
         <v>6.69</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="3">
-        <v>312904</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
-        <v>6.69</v>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="3">
+        <v>337022</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="9">
+        <v>21.99</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1618,14 +1695,14 @@
         <v>71</v>
       </c>
       <c r="C50" s="3">
-        <v>337022</v>
+        <v>308664</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
-        <v>21.99</v>
+        <v>73</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="9">
+        <v>6.99</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1633,17 +1710,17 @@
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C51" s="3">
-        <v>308664</v>
+        <v>142863</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
-        <v>6.99</v>
+        <v>75</v>
+      </c>
+      <c r="E51" s="13"/>
+      <c r="F51" s="9">
+        <v>12.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1651,17 +1728,17 @@
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C52" s="3">
-        <v>142863</v>
+        <v>100391</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7">
-        <v>12.99</v>
+        <v>77</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="9">
+        <v>2.89</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1669,17 +1746,17 @@
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C53" s="3">
-        <v>100391</v>
+        <v>156422</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
-        <v>2.89</v>
+        <v>79</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="9">
+        <v>5.99</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1690,14 +1767,14 @@
         <v>78</v>
       </c>
       <c r="C54" s="3">
-        <v>156422</v>
+        <v>321018</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="7">
-        <v>5.99</v>
+        <v>80</v>
+      </c>
+      <c r="E54" s="13"/>
+      <c r="F54" s="9">
+        <v>15.99</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1705,17 +1782,17 @@
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C55" s="3">
-        <v>321018</v>
+        <v>261176</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="7">
-        <v>15.99</v>
+        <v>82</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="9">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,14 +1803,14 @@
         <v>81</v>
       </c>
       <c r="C56" s="3">
-        <v>261176</v>
+        <v>292093</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7">
-        <v>19.989999999999998</v>
+        <v>83</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="9">
+        <v>6.99</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1744,14 +1821,14 @@
         <v>81</v>
       </c>
       <c r="C57" s="3">
-        <v>292093</v>
+        <v>259577</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="7">
-        <v>6.99</v>
+        <v>84</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="9">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1762,14 +1839,14 @@
         <v>81</v>
       </c>
       <c r="C58" s="3">
-        <v>259577</v>
+        <v>286263</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7">
-        <v>19.989999999999998</v>
+        <v>85</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="9">
+        <v>5.49</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1777,35 +1854,35 @@
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="C59" s="3">
-        <v>286263</v>
+        <v>100372</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="7">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C60" s="3">
-        <v>100372</v>
-      </c>
-      <c r="D60" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="7">
+      <c r="E59" s="13"/>
+      <c r="F59" s="9">
         <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="3">
+        <v>244424</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="9">
+        <v>13.99</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1816,14 +1893,14 @@
         <v>88</v>
       </c>
       <c r="C62" s="3">
-        <v>244424</v>
+        <v>102287</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="5"/>
-      <c r="F62" s="7">
-        <v>13.99</v>
+        <v>90</v>
+      </c>
+      <c r="E62" s="13"/>
+      <c r="F62" s="9">
+        <v>4.99</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,17 +1908,17 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C63" s="3">
-        <v>102287</v>
+        <v>286325</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="7">
-        <v>4.99</v>
+        <v>92</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="9">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1852,14 +1929,14 @@
         <v>91</v>
       </c>
       <c r="C64" s="3">
-        <v>286325</v>
+        <v>338379</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="7">
-        <v>19.989999999999998</v>
+        <v>93</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="9">
+        <v>17.989999999999998</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1870,14 +1947,14 @@
         <v>91</v>
       </c>
       <c r="C65" s="3">
-        <v>338379</v>
+        <v>308032</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="7">
-        <v>17.989999999999998</v>
+        <v>94</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="9">
+        <v>6.99</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1885,152 +1962,279 @@
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C66" s="3">
-        <v>308032</v>
+        <v>341656</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="7">
-        <v>6.99</v>
+        <v>96</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="9">
+        <v>4.49</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C67" s="3">
-        <v>191082</v>
+        <v>265726</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E67" s="5"/>
-      <c r="F67" s="7">
-        <v>31.99</v>
+        <v>98</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="9">
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>95</v>
       </c>
       <c r="C68" s="3">
+        <v>184034</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C69" s="6">
+        <v>341231</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="E69" s="15"/>
+      <c r="F69" s="11">
+        <f>15*2.89</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" s="6">
+        <v>193099</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="11">
+        <f>12*4.49</f>
+        <v>53.88</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C71" s="6">
+        <v>265727</v>
+      </c>
+      <c r="D71" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="15"/>
+      <c r="F71" s="11">
+        <f>8*4.19</f>
+        <v>33.520000000000003</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C72" s="6">
+        <v>301957</v>
+      </c>
+      <c r="D72" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E72" s="15"/>
+      <c r="F72" s="11">
+        <f>6*4.99</f>
+        <v>29.94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C73" s="6">
+        <v>324556</v>
+      </c>
+      <c r="D73" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E73" s="15"/>
+      <c r="F73" s="11">
+        <f>15*2.89</f>
+        <v>43.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C74" s="3">
+        <v>191082</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="9">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C75" s="3">
         <v>301843</v>
       </c>
-      <c r="D68" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="7">
+      <c r="D75" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E75" s="13"/>
+      <c r="F75" s="9">
         <v>77.989999999999995</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C69" s="3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C76" s="3">
         <v>102244</v>
       </c>
-      <c r="D69" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="7">
+      <c r="D76" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E76" s="13"/>
+      <c r="F76" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C70" s="3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C77" s="3">
         <v>102087</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="7">
+      <c r="D77" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E77" s="13"/>
+      <c r="F77" s="9">
         <v>49.99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C71" s="3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C78" s="3">
         <v>248750</v>
       </c>
-      <c r="D71" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E71" s="5"/>
-      <c r="F71" s="7">
+      <c r="D78" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E78" s="13"/>
+      <c r="F78" s="9">
         <v>58.99</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C72" s="3">
+    <row r="79" spans="1:6" ht="24" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C79" s="3">
         <v>297481</v>
       </c>
-      <c r="D72" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="F72" s="7">
+      <c r="D79" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C73" s="3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C80" s="3">
         <v>102036</v>
       </c>
-      <c r="D73" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E73" s="5"/>
-      <c r="F73" s="7">
+      <c r="D80" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E80" s="13"/>
+      <c r="F80" s="9">
         <v>23.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - OFERTAS ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813BFC37-4013-4C60-AF3F-A3E265D1697E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B94B1E7-6AFD-4921-B270-09B28A7BF49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -26,9 +26,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -358,7 +355,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -378,21 +375,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -436,7 +443,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -444,22 +451,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -766,1235 +783,1235 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="31" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="55.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="94.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.42578125" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100037</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="11"/>
       <c r="F2" s="7">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>335057</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="11"/>
       <c r="F3" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>199440</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="11"/>
       <c r="F4" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>117889</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="11"/>
       <c r="F5" s="7">
         <v>7.49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>279573</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>106680</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="11"/>
       <c r="F7" s="7">
         <v>8.49</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>131863</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="7">
         <v>25.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>331297</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="11"/>
       <c r="F10" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>101137</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="11"/>
       <c r="F11" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>101139</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="11"/>
       <c r="F12" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>267812</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="11"/>
       <c r="F13" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>181693</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="7">
         <v>26.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>338763</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>108494</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="7">
         <v>3.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>336566</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="7">
         <v>6.19</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>141490</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="11"/>
       <c r="F18" s="7">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>295311</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="11"/>
       <c r="F19" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>259414</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="11"/>
       <c r="F20" s="7">
         <v>2.19</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>106831</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="11"/>
       <c r="F21" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>141367</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="11"/>
       <c r="F22" s="7">
         <v>3.49</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>113543</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="11"/>
       <c r="F23" s="7">
         <v>3.49</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>112271</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>170085</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="11"/>
       <c r="F25" s="7">
         <v>25.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>271585</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>100706</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="11" t="s">
         <v>43</v>
       </c>
       <c r="F27" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>112978</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="11"/>
       <c r="F28" s="7">
         <v>3.24</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>100080</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="11"/>
       <c r="F29" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>100030</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="11"/>
       <c r="F30" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>111571</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="7">
         <v>2.59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>123142</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="11"/>
       <c r="F32" s="7">
         <v>2.19</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>149121</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="11"/>
       <c r="F33" s="7">
         <v>3.69</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>145874</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="11"/>
       <c r="F34" s="7">
         <v>10.49</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>101874</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="11"/>
       <c r="F35" s="7">
         <v>2.99</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>155079</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="11"/>
       <c r="F36" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>101083</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="11"/>
       <c r="F37" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>170363</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="11"/>
       <c r="F38" s="7">
         <v>6.59</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>108252</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="11"/>
       <c r="F39" s="7">
         <v>5.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>142447</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="11"/>
       <c r="F40" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>328759</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="11"/>
       <c r="F41" s="7">
         <v>2.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="5">
         <v>106791</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="5"/>
+      <c r="E42" s="11"/>
       <c r="F42" s="7">
         <v>2.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>274807</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="11"/>
       <c r="F43" s="7">
         <v>3.09</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>107878</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="11"/>
       <c r="F45" s="7">
         <v>4.59</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>116139</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="5"/>
+      <c r="E46" s="11"/>
       <c r="F46" s="7">
         <v>7.69</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="5">
         <v>100571</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="11"/>
       <c r="F47" s="7">
         <v>12.39</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="5">
         <v>100279</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="11"/>
       <c r="F48" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="5">
         <v>119826</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="11"/>
       <c r="F49" s="7">
         <v>2.69</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="5">
         <v>292093</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="11"/>
       <c r="F50" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="5">
         <v>326954</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="5"/>
+      <c r="E51" s="11"/>
       <c r="F51" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="5">
         <v>228234</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="11"/>
       <c r="F52" s="7">
         <v>15.49</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="5">
         <v>259568</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="E53" s="5" t="s">
+      <c r="E53" s="11" t="s">
         <v>80</v>
       </c>
       <c r="F53" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="5">
         <v>100373</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="11"/>
       <c r="F54" s="7">
         <v>24.99</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="3">
+      <c r="C56" s="5">
         <v>161871</v>
       </c>
-      <c r="D56" s="4" t="s">
+      <c r="D56" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="11"/>
       <c r="F56" s="7">
         <v>7.69</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="5">
         <v>104423</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="11"/>
       <c r="F57" s="7">
         <v>7.2</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="5">
         <v>104406</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="11"/>
       <c r="F58" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="5">
         <v>102287</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="11"/>
       <c r="F59" s="7">
         <v>4.99</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="5">
         <v>102239</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="11"/>
       <c r="F60" s="7">
         <v>25.99</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="5">
         <v>108631</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="11"/>
       <c r="F61" s="7">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="5">
         <v>157496</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="11"/>
       <c r="F62" s="7">
         <v>12.99</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="5">
         <v>302401</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="11"/>
       <c r="F63" s="7">
         <v>5.79</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="5">
         <v>341231</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="11"/>
       <c r="F64" s="7">
         <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="5">
         <v>324556</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="11"/>
       <c r="F65" s="7">
         <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C66" s="3">
+      <c r="C66" s="5">
         <v>102085</v>
       </c>
-      <c r="D66" s="4" t="s">
+      <c r="D66" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="11"/>
       <c r="F66" s="7">
         <v>13.49</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="5">
         <v>334785</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="11"/>
       <c r="F67" s="7">
         <v>149.99</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="5">
         <v>110373</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="11"/>
       <c r="F68" s="7">
         <v>109.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="5">
         <v>244831</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="5"/>
+      <c r="E69" s="11"/>
       <c r="F69" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="5">
         <v>102036</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="E70" s="5"/>
+      <c r="E70" s="11"/>
       <c r="F70" s="7">
         <v>24.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="89" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;CDE 04 A 05 DE ABRIL&amp;R&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -1,40 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AD2C01F-CA84-4B52-AF08-9183FA8A95CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E24D0AA-3400-468C-9BDA-225505F2D3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="143">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -285,6 +271,9 @@
     <t>AMACIANTE DE ROUPAS YPÊ 2L</t>
   </si>
   <si>
+    <t>ACONCHEGO, INTENSO</t>
+  </si>
+  <si>
     <t>#03 LIMPEZA - DESINFETANTES</t>
   </si>
   <si>
@@ -373,6 +362,18 @@
   </si>
   <si>
     <t>TINTURA CAPILAR BIOCOLOR MINI KIT 1UN</t>
+  </si>
+  <si>
+    <t>QUINTA/DOMINGO - ESMALTE RISQUÊ</t>
+  </si>
+  <si>
+    <t>#04 HIGIENE PESSOAL - ESMALTES</t>
+  </si>
+  <si>
+    <t>ESMALTE RISQUE 7,5ML</t>
+  </si>
+  <si>
+    <t>ESMALTE RISQUE 8ML</t>
   </si>
   <si>
     <t>#04 HIGIENE PESSOAL - HIGIENE BUCAL</t>
@@ -457,7 +458,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,8 +494,26 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -505,6 +524,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -535,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -549,6 +574,18 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -556,14 +593,8 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -867,18 +898,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="47.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,10 +922,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -914,8 +942,8 @@
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6">
+      <c r="E2" s="5"/>
+      <c r="F2" s="10">
         <v>15.99</v>
       </c>
     </row>
@@ -932,8 +960,8 @@
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6">
+      <c r="E3" s="5"/>
+      <c r="F3" s="10">
         <v>18.989999999999998</v>
       </c>
     </row>
@@ -950,8 +978,8 @@
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6">
+      <c r="E4" s="5"/>
+      <c r="F4" s="10">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -968,8 +996,8 @@
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6">
+      <c r="E5" s="5"/>
+      <c r="F5" s="10">
         <v>23.99</v>
       </c>
     </row>
@@ -986,8 +1014,8 @@
       <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6">
+      <c r="E6" s="5"/>
+      <c r="F6" s="10">
         <v>7.49</v>
       </c>
     </row>
@@ -1004,8 +1032,8 @@
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6">
+      <c r="E7" s="5"/>
+      <c r="F7" s="10">
         <v>8.99</v>
       </c>
     </row>
@@ -1022,8 +1050,8 @@
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6">
+      <c r="E8" s="5"/>
+      <c r="F8" s="10">
         <v>8.39</v>
       </c>
     </row>
@@ -1040,8 +1068,8 @@
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6">
+      <c r="E10" s="5"/>
+      <c r="F10" s="10">
         <v>7.49</v>
       </c>
     </row>
@@ -1058,8 +1086,8 @@
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6">
+      <c r="E11" s="5"/>
+      <c r="F11" s="10">
         <v>12.99</v>
       </c>
     </row>
@@ -1076,8 +1104,8 @@
       <c r="D12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6">
+      <c r="E12" s="5"/>
+      <c r="F12" s="10">
         <v>15.99</v>
       </c>
     </row>
@@ -1094,8 +1122,8 @@
       <c r="D13" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6">
+      <c r="E13" s="5"/>
+      <c r="F13" s="10">
         <v>14.99</v>
       </c>
     </row>
@@ -1112,8 +1140,8 @@
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6">
+      <c r="E14" s="5"/>
+      <c r="F14" s="10">
         <v>5.19</v>
       </c>
     </row>
@@ -1130,8 +1158,8 @@
       <c r="D15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6">
+      <c r="E15" s="5"/>
+      <c r="F15" s="10">
         <v>8.7899999999999991</v>
       </c>
     </row>
@@ -1148,8 +1176,8 @@
       <c r="D16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="6">
+      <c r="E16" s="5"/>
+      <c r="F16" s="10">
         <v>25.99</v>
       </c>
     </row>
@@ -1166,8 +1194,8 @@
       <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="6">
+      <c r="E17" s="5"/>
+      <c r="F17" s="10">
         <v>11.69</v>
       </c>
     </row>
@@ -1184,8 +1212,8 @@
       <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6">
+      <c r="E18" s="5"/>
+      <c r="F18" s="10">
         <v>6.99</v>
       </c>
     </row>
@@ -1202,8 +1230,8 @@
       <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6">
+      <c r="E19" s="5"/>
+      <c r="F19" s="10">
         <v>7.59</v>
       </c>
     </row>
@@ -1220,8 +1248,8 @@
       <c r="D20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6">
+      <c r="E20" s="5"/>
+      <c r="F20" s="10">
         <v>3.49</v>
       </c>
     </row>
@@ -1238,8 +1266,8 @@
       <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="6">
+      <c r="E21" s="5"/>
+      <c r="F21" s="10">
         <v>13.99</v>
       </c>
     </row>
@@ -1256,8 +1284,8 @@
       <c r="D22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6">
+      <c r="E22" s="5"/>
+      <c r="F22" s="10">
         <v>1.99</v>
       </c>
     </row>
@@ -1274,8 +1302,8 @@
       <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="6">
+      <c r="E23" s="5"/>
+      <c r="F23" s="10">
         <v>13.99</v>
       </c>
     </row>
@@ -1292,10 +1320,10 @@
       <c r="D24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E24" s="9" t="s">
+      <c r="E24" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="10">
         <v>2.99</v>
       </c>
     </row>
@@ -1312,8 +1340,8 @@
       <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6">
+      <c r="E25" s="5"/>
+      <c r="F25" s="10">
         <v>4.3899999999999997</v>
       </c>
     </row>
@@ -1330,8 +1358,8 @@
       <c r="D26" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6">
+      <c r="E26" s="5"/>
+      <c r="F26" s="10">
         <v>2.79</v>
       </c>
     </row>
@@ -1348,8 +1376,8 @@
       <c r="D27" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="6">
+      <c r="E27" s="5"/>
+      <c r="F27" s="10">
         <v>6.39</v>
       </c>
     </row>
@@ -1366,8 +1394,8 @@
       <c r="D28" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6">
+      <c r="E28" s="5"/>
+      <c r="F28" s="10">
         <v>5.49</v>
       </c>
     </row>
@@ -1384,8 +1412,8 @@
       <c r="D29" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6">
+      <c r="E29" s="5"/>
+      <c r="F29" s="10">
         <v>7.89</v>
       </c>
     </row>
@@ -1402,8 +1430,8 @@
       <c r="D30" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6">
+      <c r="E30" s="5"/>
+      <c r="F30" s="10">
         <v>8.99</v>
       </c>
     </row>
@@ -1420,8 +1448,8 @@
       <c r="D31" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="6">
+      <c r="E31" s="5"/>
+      <c r="F31" s="10">
         <v>4.6900000000000004</v>
       </c>
     </row>
@@ -1438,8 +1466,8 @@
       <c r="D32" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="6">
+      <c r="E32" s="5"/>
+      <c r="F32" s="10">
         <v>7.69</v>
       </c>
     </row>
@@ -1456,8 +1484,8 @@
       <c r="D33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6">
+      <c r="E33" s="5"/>
+      <c r="F33" s="10">
         <v>2.39</v>
       </c>
     </row>
@@ -1474,8 +1502,8 @@
       <c r="D34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="6">
+      <c r="E34" s="5"/>
+      <c r="F34" s="10">
         <v>3.79</v>
       </c>
     </row>
@@ -1492,8 +1520,8 @@
       <c r="D35" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="6">
+      <c r="E35" s="5"/>
+      <c r="F35" s="10">
         <v>6.99</v>
       </c>
     </row>
@@ -1510,8 +1538,8 @@
       <c r="D36" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="6">
+      <c r="E36" s="5"/>
+      <c r="F36" s="10">
         <v>7.69</v>
       </c>
     </row>
@@ -1528,8 +1556,8 @@
       <c r="D37" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="6">
+      <c r="E37" s="5"/>
+      <c r="F37" s="10">
         <v>6.69</v>
       </c>
     </row>
@@ -1546,8 +1574,8 @@
       <c r="D38" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="6">
+      <c r="E38" s="5"/>
+      <c r="F38" s="10">
         <v>7.39</v>
       </c>
     </row>
@@ -1564,8 +1592,8 @@
       <c r="D39" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="6">
+      <c r="E39" s="5"/>
+      <c r="F39" s="10">
         <v>7.39</v>
       </c>
     </row>
@@ -1582,8 +1610,8 @@
       <c r="D40" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="6">
+      <c r="E40" s="5"/>
+      <c r="F40" s="10">
         <v>7.39</v>
       </c>
     </row>
@@ -1600,8 +1628,8 @@
       <c r="D41" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="6">
+      <c r="E41" s="5"/>
+      <c r="F41" s="10">
         <v>6.99</v>
       </c>
     </row>
@@ -1618,8 +1646,8 @@
       <c r="D42" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="6">
+      <c r="E42" s="5"/>
+      <c r="F42" s="10">
         <v>2.99</v>
       </c>
     </row>
@@ -1636,8 +1664,8 @@
       <c r="D43" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="6">
+      <c r="E43" s="5"/>
+      <c r="F43" s="10">
         <v>3.09</v>
       </c>
     </row>
@@ -1654,8 +1682,8 @@
       <c r="D44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="6">
+      <c r="E44" s="5"/>
+      <c r="F44" s="10">
         <v>7.39</v>
       </c>
     </row>
@@ -1672,8 +1700,8 @@
       <c r="D45" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="6">
+      <c r="E45" s="5"/>
+      <c r="F45" s="10">
         <v>6.39</v>
       </c>
     </row>
@@ -1690,8 +1718,8 @@
       <c r="D46" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="6">
+      <c r="E46" s="5"/>
+      <c r="F46" s="10">
         <v>36.99</v>
       </c>
     </row>
@@ -1708,8 +1736,8 @@
       <c r="D47" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="6">
+      <c r="E47" s="5"/>
+      <c r="F47" s="10">
         <v>2.89</v>
       </c>
     </row>
@@ -1726,8 +1754,8 @@
       <c r="D48" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="6">
+      <c r="E48" s="5"/>
+      <c r="F48" s="10">
         <v>1.99</v>
       </c>
     </row>
@@ -1744,8 +1772,8 @@
       <c r="D49" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="6">
+      <c r="E49" s="5"/>
+      <c r="F49" s="10">
         <v>1.79</v>
       </c>
     </row>
@@ -1762,8 +1790,8 @@
       <c r="D50" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="6">
+      <c r="E50" s="5"/>
+      <c r="F50" s="10">
         <v>6.59</v>
       </c>
     </row>
@@ -1780,8 +1808,8 @@
       <c r="D52" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="6">
+      <c r="E52" s="5"/>
+      <c r="F52" s="10">
         <v>9.99</v>
       </c>
     </row>
@@ -1798,8 +1826,8 @@
       <c r="D53" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="6">
+      <c r="E53" s="5"/>
+      <c r="F53" s="10">
         <v>4.49</v>
       </c>
     </row>
@@ -1816,8 +1844,8 @@
       <c r="D54" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="6">
+      <c r="E54" s="5"/>
+      <c r="F54" s="10">
         <v>7.69</v>
       </c>
     </row>
@@ -1834,8 +1862,8 @@
       <c r="D55" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="6">
+      <c r="E55" s="5"/>
+      <c r="F55" s="10">
         <v>15.99</v>
       </c>
     </row>
@@ -1852,8 +1880,10 @@
       <c r="D56" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="9"/>
-      <c r="F56" s="6">
+      <c r="E56" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F56" s="10">
         <v>11.99</v>
       </c>
     </row>
@@ -1862,16 +1892,16 @@
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C57" s="3">
         <v>247502</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="6">
+        <v>85</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="10">
         <v>14.99</v>
       </c>
     </row>
@@ -1880,16 +1910,16 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C58" s="3">
         <v>100279</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="6">
+        <v>86</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="10">
         <v>11.99</v>
       </c>
     </row>
@@ -1898,16 +1928,16 @@
         <v>74</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C59" s="3">
         <v>123791</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="6">
+        <v>87</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="10">
         <v>11.59</v>
       </c>
     </row>
@@ -1916,16 +1946,16 @@
         <v>6</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C60" s="3">
         <v>100423</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="6">
+        <v>89</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="10">
         <v>2.69</v>
       </c>
     </row>
@@ -1934,16 +1964,16 @@
         <v>74</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C61" s="3">
         <v>200131</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="6">
+        <v>91</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="10">
         <v>49.99</v>
       </c>
     </row>
@@ -1952,16 +1982,16 @@
         <v>74</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C62" s="3">
         <v>115575</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="6">
+        <v>92</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="10">
         <v>14.99</v>
       </c>
     </row>
@@ -1970,18 +2000,18 @@
         <v>74</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C63" s="3">
         <v>118939</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E63" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="F63" s="6">
+      <c r="E63" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F63" s="10">
         <v>4.99</v>
       </c>
     </row>
@@ -1990,16 +2020,16 @@
         <v>74</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C64" s="3">
         <v>276620</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="6">
+        <v>97</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="10">
         <v>17.989999999999998</v>
       </c>
     </row>
@@ -2008,16 +2038,16 @@
         <v>74</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C65" s="3">
         <v>118935</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="6">
+        <v>99</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="10">
         <v>7.49</v>
       </c>
     </row>
@@ -2026,16 +2056,16 @@
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C66" s="3">
         <v>261360</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E66" s="9"/>
-      <c r="F66" s="6">
+        <v>101</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="10">
         <v>9.99</v>
       </c>
     </row>
@@ -2044,18 +2074,18 @@
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C67" s="3">
         <v>259568</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E67" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="F67" s="6">
+      <c r="E67" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F67" s="10">
         <v>10.49</v>
       </c>
     </row>
@@ -2064,161 +2094,161 @@
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C68" s="3">
         <v>100372</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="6">
+        <v>105</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="10">
         <v>19.989999999999998</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C70" s="3">
         <v>312361</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="6">
+        <v>108</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="10">
         <v>7.99</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C71" s="3">
         <v>213092</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="6">
+        <v>109</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="10">
         <v>7.99</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C72" s="3">
         <v>316970</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="6">
+        <v>110</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="10">
         <v>13.99</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C73" s="3">
         <v>213094</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="6">
+        <v>111</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="10">
         <v>12.99</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C74" s="3">
         <v>255029</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="6">
+        <v>112</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="10">
         <v>15.99</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C75" s="3">
         <v>215573</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="6">
+        <v>113</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="10">
         <v>12</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C76" s="3">
-        <v>272667</v>
-      </c>
-      <c r="D76" s="4" t="s">
+      <c r="A76" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="6">
-        <v>9.99</v>
+      <c r="B76" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C76" s="7">
+        <v>271863</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E76" s="8"/>
+      <c r="F76" s="12">
+        <v>4.99</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="A77" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C77" s="3">
-        <v>236651</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="6">
-        <v>15.99</v>
+      <c r="C77" s="7">
+        <v>308384</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E77" s="8"/>
+      <c r="F77" s="12">
+        <v>4.99</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -2226,71 +2256,71 @@
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C78" s="3">
-        <v>195091</v>
+        <v>272667</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="6">
-        <v>2.19</v>
+        <v>119</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="10">
+        <v>9.99</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C79" s="3">
-        <v>187000</v>
+        <v>236651</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="6">
-        <v>4.99</v>
+        <v>121</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="10">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C80" s="3">
+        <v>195091</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="10">
+        <v>2.19</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C81" s="3">
-        <v>104406</v>
+        <v>187000</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="6">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="C82" s="3">
-        <v>104410</v>
-      </c>
-      <c r="D82" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="6">
-        <v>7.99</v>
+        <v>125</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="10">
+        <v>4.99</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -2298,17 +2328,17 @@
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C83" s="3">
-        <v>102287</v>
+        <v>104406</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="6">
-        <v>4.99</v>
+        <v>127</v>
+      </c>
+      <c r="E83" s="5"/>
+      <c r="F83" s="10">
+        <v>10.89</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
@@ -2319,14 +2349,14 @@
         <v>126</v>
       </c>
       <c r="C84" s="3">
-        <v>132194</v>
+        <v>104410</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="6">
-        <v>19.989999999999998</v>
+        <v>128</v>
+      </c>
+      <c r="E84" s="5"/>
+      <c r="F84" s="10">
+        <v>7.99</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -2334,17 +2364,17 @@
         <v>6</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="C85" s="3">
-        <v>338379</v>
+        <v>102287</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="6">
-        <v>16.989999999999998</v>
+        <v>130</v>
+      </c>
+      <c r="E85" s="5"/>
+      <c r="F85" s="10">
+        <v>4.99</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -2352,117 +2382,149 @@
         <v>6</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C86" s="3">
+        <v>132194</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E86" s="5"/>
+      <c r="F86" s="10">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C87" s="3">
+        <v>338379</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E87" s="5"/>
+      <c r="F87" s="10">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C88" s="7">
         <v>298701</v>
       </c>
-      <c r="D86" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="6">
+      <c r="D88" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="E88" s="8"/>
+      <c r="F88" s="12">
         <f>12*3.89</f>
         <v>46.68</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C87" s="3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C89" s="7">
         <v>341231</v>
       </c>
-      <c r="D87" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="6">
-        <f>15*(2.89)</f>
+      <c r="D89" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E89" s="8"/>
+      <c r="F89" s="12">
+        <f>15*2.89</f>
         <v>43.35</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C88" s="3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C90" s="7">
         <v>324556</v>
       </c>
-      <c r="D88" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E88" s="9"/>
-      <c r="F88" s="6">
+      <c r="D90" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="E90" s="8"/>
+      <c r="F90" s="12">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C89" s="3">
-        <v>206930</v>
-      </c>
-      <c r="D89" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="E89" s="9"/>
-      <c r="F89" s="6">
-        <v>140.99</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C90" s="3">
-        <v>109729</v>
-      </c>
-      <c r="D90" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="E90" s="9"/>
-      <c r="F90" s="6">
-        <v>97.99</v>
-      </c>
-    </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C91" s="3">
+        <v>206930</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="E91" s="5"/>
+      <c r="F91" s="10">
+        <v>140.99</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C92" s="3">
+        <v>109729</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E92" s="5"/>
+      <c r="F92" s="10">
+        <v>97.99</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C93" s="3">
         <v>139964</v>
       </c>
-      <c r="D91" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="6">
+      <c r="D93" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="10">
         <v>26.99</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" r:id="rId1"/>
-  <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS &amp;C&amp;P - &amp;N</oddHeader>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDD5AB7A-35B8-41B3-9618-4259FB1DBA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C31D6220-7251-4672-91C1-57698150DCDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,7 +410,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -430,21 +430,31 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
+      <b/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -488,7 +498,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -496,28 +506,32 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -824,1525 +838,1525 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F87"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="37.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.28515625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="75" style="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>100020</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="6">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>199440</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>301961</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>342706</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>279573</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>106680</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="6">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>8.39</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>158013</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>1.69</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="6">
         <v>132716</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6">
+      <c r="E10" s="8"/>
+      <c r="F10" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>318330</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>101136</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="6">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>174298</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="6">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>14.69</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>261728</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="6">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>267812</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="6">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>199869</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="6">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>181693</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="6">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>25.99</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>174071</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="6">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>273714</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="6">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>7.69</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>100780</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="6">
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>3.59</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>111516</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="9" t="s">
+      <c r="E21" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>321107</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="6">
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>1.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>106831</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="9" t="s">
+      <c r="E23" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>141367</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="6">
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>112271</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="6">
+      <c r="E25" s="8"/>
+      <c r="F25" s="9">
         <v>4.49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>186561</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="9"/>
-      <c r="F26" s="6">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>34.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>106854</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E27" s="9" t="s">
+      <c r="E27" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="9">
         <v>11.59</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>112978</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E28" s="9"/>
-      <c r="F28" s="6">
+      <c r="E28" s="8"/>
+      <c r="F28" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>109159</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E29" s="9"/>
-      <c r="F29" s="6">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>7.59</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>134629</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="6">
+      <c r="E30" s="8"/>
+      <c r="F30" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>167187</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="6">
+      <c r="E31" s="8"/>
+      <c r="F31" s="9">
         <v>22.99</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>313827</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="6">
+      <c r="E32" s="8"/>
+      <c r="F32" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>101066</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="6">
+      <c r="E33" s="8"/>
+      <c r="F33" s="9">
         <v>3.09</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>101083</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="6">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9">
         <v>7.19</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>142446</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="6">
+      <c r="E35" s="8"/>
+      <c r="F35" s="9">
         <v>6.19</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
         <v>183340</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="6">
+      <c r="E36" s="8"/>
+      <c r="F36" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>307145</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="6">
+      <c r="E37" s="8"/>
+      <c r="F37" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>113818</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="6">
+      <c r="E38" s="8"/>
+      <c r="F38" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="6">
         <v>328759</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E39" s="9"/>
-      <c r="F39" s="6">
+      <c r="E39" s="8"/>
+      <c r="F39" s="9">
         <v>1.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="6">
         <v>108414</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E40" s="9"/>
-      <c r="F40" s="6">
+      <c r="E40" s="8"/>
+      <c r="F40" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C42" s="3">
+      <c r="C42" s="6">
         <v>130159</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E42" s="9"/>
-      <c r="F42" s="6">
+      <c r="E42" s="8"/>
+      <c r="F42" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
         <v>100426</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="6">
+      <c r="E43" s="8"/>
+      <c r="F43" s="9">
         <v>3.79</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="6">
         <v>100430</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="6">
+      <c r="E44" s="8"/>
+      <c r="F44" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="6">
         <v>133368</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="9"/>
-      <c r="F45" s="6">
+      <c r="E45" s="8"/>
+      <c r="F45" s="9">
         <v>16.989999999999998</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="6">
         <v>285689</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E46" s="9"/>
-      <c r="F46" s="6">
+      <c r="E46" s="8"/>
+      <c r="F46" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="6">
         <v>107393</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="6">
+      <c r="E47" s="8"/>
+      <c r="F47" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="6">
         <v>100279</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E48" s="9"/>
-      <c r="F48" s="6">
+      <c r="E48" s="8"/>
+      <c r="F48" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="6">
         <v>100391</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="6">
+      <c r="E49" s="8"/>
+      <c r="F49" s="9">
         <v>2.89</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="6">
         <v>100511</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="6">
+      <c r="E50" s="8"/>
+      <c r="F50" s="9">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="6">
         <v>191636</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="6">
+      <c r="E51" s="8"/>
+      <c r="F51" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C52" s="3">
+      <c r="C52" s="6">
         <v>257710</v>
       </c>
-      <c r="D52" s="4" t="s">
+      <c r="D52" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="6">
+      <c r="E52" s="8"/>
+      <c r="F52" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="6">
         <v>215454</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="6">
+      <c r="E53" s="8"/>
+      <c r="F53" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C54" s="3">
+      <c r="C54" s="6">
         <v>286263</v>
       </c>
-      <c r="D54" s="4" t="s">
+      <c r="D54" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="6">
+      <c r="E54" s="8"/>
+      <c r="F54" s="9">
         <v>5.69</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C55" s="3">
+      <c r="C55" s="6">
         <v>100372</v>
       </c>
-      <c r="D55" s="4" t="s">
+      <c r="D55" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E55" s="9"/>
-      <c r="F55" s="6">
+      <c r="E55" s="8"/>
+      <c r="F55" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C57" s="3">
+      <c r="C57" s="6">
         <v>312361</v>
       </c>
-      <c r="D57" s="4" t="s">
+      <c r="D57" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="6">
+      <c r="E57" s="8"/>
+      <c r="F57" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C58" s="3">
+      <c r="C58" s="6">
         <v>213092</v>
       </c>
-      <c r="D58" s="4" t="s">
+      <c r="D58" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="E58" s="9"/>
-      <c r="F58" s="6">
+      <c r="E58" s="8"/>
+      <c r="F58" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C59" s="3">
+      <c r="C59" s="6">
         <v>316970</v>
       </c>
-      <c r="D59" s="4" t="s">
+      <c r="D59" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="6">
+      <c r="E59" s="8"/>
+      <c r="F59" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C60" s="3">
+      <c r="C60" s="6">
         <v>213094</v>
       </c>
-      <c r="D60" s="4" t="s">
+      <c r="D60" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="6">
+      <c r="E60" s="8"/>
+      <c r="F60" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C61" s="3">
+      <c r="C61" s="6">
         <v>197021</v>
       </c>
-      <c r="D61" s="4" t="s">
+      <c r="D61" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="6">
+      <c r="E61" s="8"/>
+      <c r="F61" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C62" s="3">
+      <c r="C62" s="6">
         <v>255029</v>
       </c>
-      <c r="D62" s="4" t="s">
+      <c r="D62" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="6">
+      <c r="E62" s="8"/>
+      <c r="F62" s="9">
         <v>15.99</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C63" s="3">
+      <c r="C63" s="6">
         <v>215573</v>
       </c>
-      <c r="D63" s="4" t="s">
+      <c r="D63" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="6">
+      <c r="E63" s="8"/>
+      <c r="F63" s="9">
         <v>12</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="3">
+      <c r="C64" s="6">
         <v>216127</v>
       </c>
-      <c r="D64" s="4" t="s">
+      <c r="D64" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="6">
+      <c r="E64" s="8"/>
+      <c r="F64" s="9">
         <v>3.69</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>86</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="3">
+      <c r="C65" s="6">
         <v>187000</v>
       </c>
-      <c r="D65" s="4" t="s">
+      <c r="D65" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E65" s="9"/>
-      <c r="F65" s="6">
+      <c r="E65" s="8"/>
+      <c r="F65" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C67" s="3">
+      <c r="C67" s="6">
         <v>315426</v>
       </c>
-      <c r="D67" s="4" t="s">
+      <c r="D67" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="6">
+      <c r="E67" s="8"/>
+      <c r="F67" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C68" s="3">
+      <c r="C68" s="6">
         <v>104412</v>
       </c>
-      <c r="D68" s="4" t="s">
+      <c r="D68" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="E68" s="9"/>
-      <c r="F68" s="6">
+      <c r="E68" s="8"/>
+      <c r="F68" s="9">
         <v>9.9</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C69" s="3">
+      <c r="C69" s="6">
         <v>108686</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D69" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E69" s="9"/>
-      <c r="F69" s="6">
+      <c r="E69" s="8"/>
+      <c r="F69" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C70" s="3">
+      <c r="C70" s="6">
         <v>104406</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E70" s="9"/>
-      <c r="F70" s="6">
+      <c r="E70" s="8"/>
+      <c r="F70" s="9">
         <v>10.49</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C71" s="3">
+      <c r="C71" s="6">
         <v>104404</v>
       </c>
-      <c r="D71" s="4" t="s">
+      <c r="D71" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="6">
+      <c r="E71" s="8"/>
+      <c r="F71" s="9">
         <v>9.49</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C72" s="3">
+      <c r="C72" s="6">
         <v>104410</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D72" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E72" s="9"/>
-      <c r="F72" s="6">
+      <c r="E72" s="8"/>
+      <c r="F72" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C73" s="3">
+      <c r="C73" s="6">
         <v>335090</v>
       </c>
-      <c r="D73" s="4" t="s">
+      <c r="D73" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="6">
+      <c r="E73" s="8"/>
+      <c r="F73" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C74" s="3">
+      <c r="C74" s="6">
         <v>102282</v>
       </c>
-      <c r="D74" s="4" t="s">
+      <c r="D74" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="6">
+      <c r="E74" s="8"/>
+      <c r="F74" s="9">
         <v>9</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C75" s="3">
+      <c r="C75" s="6">
         <v>102237</v>
       </c>
-      <c r="D75" s="4" t="s">
+      <c r="D75" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="6">
+      <c r="E75" s="8"/>
+      <c r="F75" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C76" s="3">
+      <c r="C76" s="6">
         <v>102149</v>
       </c>
-      <c r="D76" s="4" t="s">
+      <c r="D76" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="6">
+      <c r="E76" s="8"/>
+      <c r="F76" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C77" s="3">
+      <c r="C77" s="6">
         <v>298700</v>
       </c>
-      <c r="D77" s="4" t="s">
+      <c r="D77" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E77" s="9"/>
-      <c r="F77" s="6">
+      <c r="E77" s="8"/>
+      <c r="F77" s="9">
         <v>3.79</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C78" s="3">
+      <c r="C78" s="6">
         <v>247799</v>
       </c>
-      <c r="D78" s="4" t="s">
+      <c r="D78" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="E78" s="9"/>
-      <c r="F78" s="6">
+      <c r="E78" s="8"/>
+      <c r="F78" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C79" s="3">
+      <c r="C79" s="6">
         <v>325999</v>
       </c>
-      <c r="D79" s="4" t="s">
+      <c r="D79" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="E79" s="9"/>
-      <c r="F79" s="6">
+      <c r="E79" s="8"/>
+      <c r="F79" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C80" s="3">
+      <c r="C80" s="6">
         <v>244191</v>
       </c>
-      <c r="D80" s="4" t="s">
+      <c r="D80" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E80" s="9"/>
-      <c r="F80" s="6">
+      <c r="E80" s="8"/>
+      <c r="F80" s="9">
         <v>6.89</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C81" s="3">
+      <c r="C81" s="6">
         <v>341231</v>
       </c>
-      <c r="D81" s="4" t="s">
+      <c r="D81" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="E81" s="9"/>
-      <c r="F81" s="6">
+      <c r="E81" s="8"/>
+      <c r="F81" s="9">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C82" s="3">
+      <c r="C82" s="6">
         <v>170451</v>
       </c>
-      <c r="D82" s="4" t="s">
+      <c r="D82" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="E82" s="9"/>
-      <c r="F82" s="6">
+      <c r="E82" s="8"/>
+      <c r="F82" s="9">
         <f>15*3.09</f>
         <v>46.349999999999994</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C83" s="3">
+      <c r="C83" s="6">
         <v>102085</v>
       </c>
-      <c r="D83" s="4" t="s">
+      <c r="D83" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="E83" s="9"/>
-      <c r="F83" s="6">
+      <c r="E83" s="8"/>
+      <c r="F83" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C84" s="6">
         <v>301843</v>
       </c>
-      <c r="D84" s="4" t="s">
+      <c r="D84" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E84" s="9"/>
-      <c r="F84" s="6">
+      <c r="E84" s="8"/>
+      <c r="F84" s="9">
         <v>78.989999999999995</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C85" s="6">
         <v>109727</v>
       </c>
-      <c r="D85" s="4" t="s">
+      <c r="D85" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="E85" s="9"/>
-      <c r="F85" s="6">
+      <c r="E85" s="8"/>
+      <c r="F85" s="9">
         <v>189.99</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C86" s="3">
+      <c r="C86" s="6">
         <v>109729</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="E86" s="9"/>
-      <c r="F86" s="6">
+      <c r="E86" s="8"/>
+      <c r="F86" s="9">
         <v>99.99</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C87" s="3">
+      <c r="C87" s="6">
         <v>139964</v>
       </c>
-      <c r="D87" s="4" t="s">
+      <c r="D87" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E87" s="9"/>
-      <c r="F87" s="6">
+      <c r="E87" s="8"/>
+      <c r="F87" s="9">
         <v>27.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - QUINTA A DOMINGO&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF414C33-75E5-49E2-BDF9-63C3DE605C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ACFB21E-0D40-4DD9-98E7-9941C41AC6C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,9 +223,6 @@
     <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
   </si>
   <si>
-    <t>AMACIANTE DE ROUPAS DOWNY CONC 500ML BRISA SUAVE</t>
-  </si>
-  <si>
     <t>#03 LIMPEZA - DESINFETANTES</t>
   </si>
   <si>
@@ -335,6 +332,9 @@
   </si>
   <si>
     <t>WHISKY WHITE HORSE 1L</t>
+  </si>
+  <si>
+    <t>AMACIANTE DE ROUPAS DOWNY CONCENTRADO 500ML BRISA SUAVE</t>
   </si>
 </sst>
 </file>
@@ -344,7 +344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -354,31 +354,30 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="7"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -427,25 +426,23 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -752,17 +749,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F69"/>
-  <sheetFormatPr defaultRowHeight="19.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="28.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.85546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="90.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -778,1167 +776,1167 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="5">
         <v>100038</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
+      <c r="E2" s="6"/>
       <c r="F2" s="7">
         <v>24.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="5">
         <v>325990</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
+      <c r="E3" s="6"/>
       <c r="F3" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="5">
         <v>225003</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="6"/>
       <c r="F4" s="7">
         <v>20.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="5">
         <v>345404</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="7">
         <v>6.89</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="5">
         <v>163918</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="7">
         <v>11.19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="5">
         <v>165928</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5"/>
+      <c r="E7" s="6"/>
       <c r="F7" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="5">
         <v>167128</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="5"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="7">
         <v>8.59</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="5">
         <v>255232</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="7">
         <v>22.79</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="5">
         <v>101137</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="7">
         <v>16.59</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="5">
         <v>261728</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="7">
         <v>8.59</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="5">
         <v>297642</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
+      <c r="E13" s="6"/>
       <c r="F13" s="7">
         <v>4.29</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="5">
         <v>286197</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="6"/>
       <c r="F14" s="7">
         <v>8.69</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="5">
         <v>200781</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="5"/>
+      <c r="E15" s="6"/>
       <c r="F15" s="7">
         <v>15.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="5">
         <v>336113</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
+      <c r="E16" s="6"/>
       <c r="F16" s="7">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A17" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="5">
         <v>253532</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
+      <c r="E17" s="6"/>
       <c r="F17" s="7">
         <v>8.69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="2" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A18" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="5">
         <v>100780</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="5"/>
+      <c r="E18" s="6"/>
       <c r="F18" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" s="2" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="5">
         <v>101728</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="5"/>
+      <c r="E19" s="6"/>
       <c r="F19" s="7">
         <v>13.59</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="2" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A20" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="5">
         <v>120921</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="5"/>
+      <c r="E20" s="6"/>
       <c r="F20" s="7">
         <v>23.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="2" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A21" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="5">
         <v>115548</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="E21" s="6"/>
       <c r="F21" s="7">
         <v>1.19</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="2" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A22" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="5">
         <v>148270</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="5"/>
+      <c r="E22" s="6"/>
       <c r="F22" s="7">
         <v>3.59</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="2" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A23" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="5">
         <v>106961</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="E23" s="5"/>
+      <c r="E23" s="6"/>
       <c r="F23" s="7">
         <v>3.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="2" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A24" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="5">
         <v>107640</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="5"/>
+      <c r="E24" s="6"/>
       <c r="F24" s="7">
         <v>4.49</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="2" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="5">
         <v>100705</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="5"/>
+      <c r="E25" s="6"/>
       <c r="F25" s="7">
         <v>7.59</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A26" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="5">
         <v>112978</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="5"/>
+      <c r="E26" s="6"/>
       <c r="F26" s="7">
         <v>2.89</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A27" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="5">
         <v>128930</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="5"/>
+      <c r="E27" s="6"/>
       <c r="F27" s="7">
         <v>6.59</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="2" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A28" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="5">
         <v>107361</v>
       </c>
       <c r="D28" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="5"/>
+      <c r="E28" s="6"/>
       <c r="F28" s="7">
         <v>5.69</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="2" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A29" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="5">
         <v>100024</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="5"/>
+      <c r="E29" s="6"/>
       <c r="F29" s="7">
         <v>5.49</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="2" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A30" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="5">
         <v>286277</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="5"/>
+      <c r="E30" s="6"/>
       <c r="F30" s="7">
         <v>2.79</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="2" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A31" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="5">
         <v>101130</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="5"/>
+      <c r="E31" s="6"/>
       <c r="F31" s="7">
         <v>8.19</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A32" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="5">
         <v>128920</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="5"/>
+      <c r="E32" s="6"/>
       <c r="F32" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="2" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A33" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="5">
         <v>101874</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="5"/>
+      <c r="E33" s="6"/>
       <c r="F33" s="7">
         <v>3.19</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="2" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A34" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="5">
         <v>193295</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E34" s="5"/>
+      <c r="E34" s="6"/>
       <c r="F34" s="7">
         <v>3.89</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A35" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="5">
         <v>155080</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E35" s="5"/>
+      <c r="E35" s="6"/>
       <c r="F35" s="7">
         <v>7.19</v>
       </c>
     </row>
-    <row r="36" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="2" t="s">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A36" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="5">
         <v>101113</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="E36" s="5"/>
+      <c r="E36" s="6"/>
       <c r="F36" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A37" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="5">
         <v>251877</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E37" s="5"/>
+      <c r="E37" s="6"/>
       <c r="F37" s="7">
         <v>20.79</v>
       </c>
     </row>
-    <row r="38" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A38" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="5">
         <v>307145</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="5"/>
+      <c r="E38" s="6"/>
       <c r="F38" s="7">
         <v>20.89</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="2" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="5">
         <v>303196</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E39" s="5"/>
+      <c r="E39" s="6"/>
       <c r="F39" s="7">
         <v>3.49</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="2" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="5">
         <v>163423</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="E40" s="5"/>
+      <c r="E40" s="6"/>
       <c r="F40" s="7">
         <v>6.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="5">
         <v>274807</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="5"/>
+      <c r="E41" s="6"/>
       <c r="F41" s="7">
         <v>2.69</v>
       </c>
     </row>
-    <row r="43" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B43" s="2" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A43" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="5">
         <v>207640</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="E43" s="5"/>
+      <c r="E43" s="6"/>
       <c r="F43" s="7">
         <v>7.59</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A44" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="5">
         <v>100426</v>
       </c>
       <c r="D44" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="5"/>
+      <c r="E44" s="6"/>
       <c r="F44" s="7">
         <v>4.49</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A45" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="5">
         <v>133368</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="5"/>
+      <c r="E45" s="6"/>
       <c r="F45" s="7">
         <v>20.69</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="2" t="s">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="5">
         <v>302655</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E46" s="5"/>
+        <v>104</v>
+      </c>
+      <c r="E46" s="6"/>
       <c r="F46" s="7">
         <v>11.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A47" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="5">
+        <v>110507</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="C47" s="3">
-        <v>110507</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="5"/>
+      <c r="E47" s="6"/>
       <c r="F47" s="7">
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="48" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A48" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C48" s="5">
+        <v>100403</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C48" s="3">
-        <v>100403</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="E48" s="5"/>
+      <c r="E48" s="6"/>
       <c r="F48" s="7">
         <v>3.39</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="2" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A49" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C49" s="5">
+        <v>100511</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="3">
-        <v>100511</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="5"/>
+      <c r="E49" s="6"/>
       <c r="F49" s="7">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A50" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50" s="5">
+        <v>257710</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="3">
-        <v>257710</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E50" s="5"/>
+      <c r="E50" s="6"/>
       <c r="F50" s="7">
         <v>11.39</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A51" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C51" s="5">
         <v>261980</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="E51" s="5"/>
+        <v>75</v>
+      </c>
+      <c r="E51" s="6"/>
       <c r="F51" s="7">
         <v>18.79</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="2" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A52" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C52" s="5">
+        <v>135352</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="C52" s="3">
-        <v>135352</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E52" s="5"/>
+      <c r="E52" s="6"/>
       <c r="F52" s="7">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="2" t="s">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C54" s="5">
+        <v>120010</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="3">
-        <v>120010</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="6"/>
       <c r="F54" s="7">
         <v>10.69</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="2" t="s">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C55" s="5">
+        <v>107928</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C55" s="3">
-        <v>107928</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="6"/>
       <c r="F55" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="2" t="s">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C56" s="5">
+        <v>256740</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C56" s="3">
-        <v>256740</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="6"/>
       <c r="F56" s="7">
         <v>10.19</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C57" s="5">
         <v>182485</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E57" s="5"/>
+        <v>84</v>
+      </c>
+      <c r="E57" s="6"/>
       <c r="F57" s="7">
         <v>8.99</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="2" t="s">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A58" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C58" s="5">
+        <v>219705</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="C58" s="3">
-        <v>219705</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="6"/>
       <c r="F58" s="7">
         <v>21.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="2" t="s">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A59" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="5">
+        <v>157417</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C59" s="3">
-        <v>157417</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="6"/>
       <c r="F59" s="7">
         <v>3.89</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B61" s="2" t="s">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A61" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61" s="5">
+        <v>104406</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="C61" s="3">
-        <v>104406</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="6"/>
       <c r="F61" s="7">
         <v>10.99</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C62" s="3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A62" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C62" s="5">
         <v>104410</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E62" s="5"/>
+        <v>91</v>
+      </c>
+      <c r="E62" s="6"/>
       <c r="F62" s="7">
         <v>7.39</v>
       </c>
     </row>
-    <row r="63" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="2" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A63" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C63" s="5">
+        <v>117100</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="C63" s="3">
-        <v>117100</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="6"/>
       <c r="F63" s="7">
         <v>10.19</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A64" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C64" s="5">
+        <v>286325</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C64" s="3">
-        <v>286325</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="6"/>
       <c r="F64" s="7">
         <v>20.190000000000001</v>
       </c>
     </row>
-    <row r="65" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="s">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A65" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C65" s="5">
+        <v>267604</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C65" s="3">
-        <v>267604</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="6"/>
       <c r="F65" s="7">
         <v>6.19</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="2" t="s">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A66" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C66" s="5">
+        <v>258893</v>
+      </c>
+      <c r="D66" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="C66" s="3">
-        <v>258893</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="6"/>
       <c r="F66" s="7">
         <f>15*4.09</f>
         <v>61.349999999999994</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C67" s="3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A67" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C67" s="5">
         <v>324556</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E67" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="E67" s="6"/>
       <c r="F67" s="7">
         <f>15*3.09</f>
         <v>46.349999999999994</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="2" t="s">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A68" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C68" s="5">
+        <v>102085</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C68" s="3">
-        <v>102085</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="6"/>
       <c r="F68" s="7">
         <v>13.99</v>
       </c>
     </row>
-    <row r="69" spans="1:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C69" s="3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A69" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C69" s="5">
         <v>109729</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E69" s="5"/>
+        <v>103</v>
+      </c>
+      <c r="E69" s="6"/>
       <c r="F69" s="7">
         <v>89.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>

--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D9E836-5B2B-44DC-BDD8-0C71DA38A915}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7089F24-CE8D-4EDD-9598-054A75E311D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
     <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
   </si>
   <si>
-    <t>CAFÉ MARATA 250G TRADICIONAL</t>
+    <t>CAFÉ SANTA CLARA 250G CLASSICO</t>
   </si>
   <si>
     <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
@@ -287,7 +287,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,24 +307,47 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -335,6 +358,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -373,22 +402,38 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -695,888 +740,888 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F53"/>
-  <sheetFormatPr defaultColWidth="35.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="40.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="42.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="42.140625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="38.85546875" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="100.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>199439</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>225003</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="6">
         <v>298239</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>6.89</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>163918</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>11.49</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="6">
         <v>106680</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>8.69</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>228421</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>46.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>255232</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="8"/>
+      <c r="F9" s="9">
         <v>22.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="3">
-        <v>101137</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="10">
+        <v>114037</v>
+      </c>
+      <c r="D10" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="11"/>
+      <c r="F10" s="12">
+        <v>15.49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="6">
         <v>267812</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>262479</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>239315</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>181693</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="8"/>
+      <c r="F14" s="9">
         <v>28.99</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="2" t="s">
+    <row r="15" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="10">
         <v>228310</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="7">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E15" s="11"/>
+      <c r="F15" s="12">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="6">
         <v>100876</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>100884</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>5.69</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>106960</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>221945</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>5.19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>112978</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>193449</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="8"/>
+      <c r="F21" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>155501</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>5.29</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>100120</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>2.4900000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>168910</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>5.89</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>107118</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="8"/>
+      <c r="F25" s="9">
         <v>3.19</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>108434</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>8.39</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>142446</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="8"/>
+      <c r="F27" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>207638</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>116139</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="8"/>
+      <c r="F30" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C31" s="3">
+      <c r="C31" s="6">
         <v>247502</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
+      <c r="E31" s="8"/>
+      <c r="F31" s="9">
         <v>22.59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C32" s="3">
+      <c r="C32" s="6">
         <v>100423</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
+      <c r="E32" s="8"/>
+      <c r="F32" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="3">
+      <c r="C33" s="6">
         <v>204688</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
+      <c r="E33" s="8"/>
+      <c r="F33" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C34" s="3">
+      <c r="C34" s="6">
         <v>261083</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C35" s="3">
+      <c r="C35" s="6">
         <v>100373</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
+      <c r="E35" s="8"/>
+      <c r="F35" s="9">
         <v>26.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="3">
+      <c r="C37" s="6">
         <v>297599</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="E37" s="8"/>
+      <c r="F37" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C38" s="3">
+      <c r="C38" s="6">
         <v>256740</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="E38" s="8"/>
+      <c r="F38" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C39" s="3">
+      <c r="C39" s="6">
         <v>199322</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="E39" s="8"/>
+      <c r="F39" s="9">
         <v>11.59</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C40" s="3">
+      <c r="C40" s="6">
         <v>205206</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
+      <c r="E40" s="8"/>
+      <c r="F40" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="3">
+      <c r="C41" s="6">
         <v>144261</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
+      <c r="E41" s="8"/>
+      <c r="F41" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>69</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
         <v>317964</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="E43" s="8"/>
+      <c r="F43" s="9">
         <v>1.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="3">
+      <c r="C44" s="6">
         <v>104406</v>
       </c>
-      <c r="D44" s="4" t="s">
+      <c r="D44" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="7">
+      <c r="E44" s="8"/>
+      <c r="F44" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C45" s="3">
+      <c r="C45" s="6">
         <v>102287</v>
       </c>
-      <c r="D45" s="4" t="s">
+      <c r="D45" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="E45" s="8"/>
+      <c r="F45" s="9">
         <v>5.29</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C46" s="3">
+      <c r="C46" s="6">
         <v>286325</v>
       </c>
-      <c r="D46" s="4" t="s">
+      <c r="D46" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="E46" s="8"/>
+      <c r="F46" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C47" s="3">
+      <c r="C47" s="10">
         <v>324556</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="11" t="s">
         <v>78</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="E47" s="11"/>
+      <c r="F47" s="12">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C48" s="3">
+      <c r="C48" s="6">
         <v>149113</v>
       </c>
-      <c r="D48" s="4" t="s">
+      <c r="D48" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
+      <c r="E48" s="8"/>
+      <c r="F48" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="3">
+      <c r="C49" s="6">
         <v>102242</v>
       </c>
-      <c r="D49" s="4" t="s">
+      <c r="D49" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="E49" s="8"/>
+      <c r="F49" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C50" s="3">
+      <c r="C50" s="6">
         <v>102077</v>
       </c>
-      <c r="D50" s="4" t="s">
+      <c r="D50" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
+      <c r="E50" s="8"/>
+      <c r="F50" s="9">
         <v>174.99</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C51" s="3">
+      <c r="C51" s="6">
         <v>109729</v>
       </c>
-      <c r="D51" s="4" t="s">
+      <c r="D51" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="E51" s="8"/>
+      <c r="F51" s="9">
         <v>95.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C53" s="3">
+      <c r="C53" s="6">
         <v>101817</v>
       </c>
-      <c r="D53" s="4" t="s">
+      <c r="D53" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E53" s="5"/>
-      <c r="F53" s="7">
+      <c r="E53" s="8"/>
+      <c r="F53" s="9">
         <v>25.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="94" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - QUINTA A SABADO&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12E0D7D-9FA7-4371-A274-65F6CFA7EF8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC199DD8-8EEB-49AB-90A9-E457C98A8A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="110">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>CUSCUZ DE MILHO SABOR DO PARA 500G</t>
+  </si>
+  <si>
+    <t>CUSCUZ DE MILHO SINHA 500G</t>
   </si>
   <si>
     <t>FARINHA DE MANDIOCA BIJU AMAFIL 500G TORRADA</t>
@@ -371,53 +374,48 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="7"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="7"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="7"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="8"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -470,55 +468,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -827,1270 +821,1288 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
-  <sheetFormatPr defaultRowHeight="44.25" customHeight="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F74"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="43.5703125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="100.7109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.7109375" style="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="17" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7">
+      <c r="C2" s="3">
         <v>229173</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="9"/>
-      <c r="F2" s="10">
+      <c r="E2" s="13"/>
+      <c r="F2" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="3">
         <v>141640</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="E3" s="13"/>
-      <c r="F3" s="14">
+      <c r="F3" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="3">
         <v>199440</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="10">
+      <c r="E4" s="13"/>
+      <c r="F4" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="3">
         <v>327443</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="10">
+      <c r="E5" s="13"/>
+      <c r="F5" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="3">
         <v>140665</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="10">
+      <c r="E6" s="13"/>
+      <c r="F6" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="6">
         <v>106680</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="14"/>
       <c r="F7" s="10">
-        <v>8.59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="3">
         <v>345404</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="10">
+      <c r="E8" s="13"/>
+      <c r="F8" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="3">
         <v>104679</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E10" s="13"/>
-      <c r="F10" s="14">
+      <c r="F10" s="9">
         <v>3.19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="3">
         <v>344310</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="10">
+      <c r="E11" s="13"/>
+      <c r="F11" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="6">
         <v>101137</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="14"/>
       <c r="F12" s="10">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="3">
         <v>110372</v>
       </c>
-      <c r="D13" s="8" t="s">
+      <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="10">
+      <c r="E13" s="13"/>
+      <c r="F13" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="3">
         <v>261728</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="13"/>
-      <c r="F14" s="14">
+      <c r="F14" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="3">
         <v>199869</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="4" t="s">
         <v>25</v>
       </c>
       <c r="E15" s="13"/>
-      <c r="F15" s="14">
+      <c r="F15" s="9">
         <v>8.49</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="3">
         <v>263132</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E16" s="13"/>
-      <c r="F16" s="14">
+      <c r="F16" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="3" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="3">
         <v>280720</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="4" t="s">
         <v>28</v>
       </c>
       <c r="E17" s="13"/>
-      <c r="F17" s="14">
+      <c r="F17" s="9">
         <v>5.39</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="3">
         <v>327574</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E18" s="13"/>
-      <c r="F18" s="14">
+      <c r="F18" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="7">
+      <c r="C19" s="3">
         <v>253531</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="10">
+      <c r="E19" s="13"/>
+      <c r="F19" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="3">
         <v>343468</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="4" t="s">
         <v>31</v>
       </c>
       <c r="E20" s="13"/>
-      <c r="F20" s="14">
+      <c r="F20" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="3">
         <v>147187</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="4" t="s">
         <v>32</v>
       </c>
       <c r="E21" s="13"/>
-      <c r="F21" s="14">
+      <c r="F21" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C22" s="3">
         <v>273714</v>
       </c>
-      <c r="D22" s="8" t="s">
+      <c r="D22" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="10">
+      <c r="E22" s="13"/>
+      <c r="F22" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="3">
         <v>287073</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="E23" s="13"/>
-      <c r="F23" s="14">
+      <c r="F23" s="9">
         <v>2.29</v>
       </c>
     </row>
-    <row r="24" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" s="3" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="3">
         <v>100872</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="4" t="s">
         <v>35</v>
       </c>
       <c r="E24" s="13"/>
-      <c r="F24" s="14">
+      <c r="F24" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B25" s="3" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="3">
         <v>109390</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="4" t="s">
         <v>36</v>
       </c>
       <c r="E25" s="13"/>
-      <c r="F25" s="14">
+      <c r="F25" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="26" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="3" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="3">
         <v>113543</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="4" t="s">
         <v>37</v>
       </c>
       <c r="E26" s="13"/>
-      <c r="F26" s="14">
+      <c r="F26" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="3" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="3">
         <v>106781</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="4" t="s">
         <v>39</v>
       </c>
       <c r="E27" s="13"/>
-      <c r="F27" s="14">
+      <c r="F27" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="28" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="3">
         <v>234316</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="4" t="s">
         <v>41</v>
       </c>
       <c r="E28" s="13"/>
-      <c r="F28" s="14">
+      <c r="F28" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="3">
         <v>207321</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="4" t="s">
         <v>43</v>
       </c>
       <c r="E29" s="13"/>
-      <c r="F29" s="14">
+      <c r="F29" s="9">
         <v>15.49</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="3" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="3">
         <v>301367</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="4" t="s">
         <v>44</v>
       </c>
       <c r="E30" s="13"/>
-      <c r="F30" s="14">
+      <c r="F30" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="3">
         <v>262643</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="4" t="s">
         <v>46</v>
       </c>
       <c r="E31" s="13"/>
-      <c r="F31" s="14">
+      <c r="F31" s="9">
         <v>2.59</v>
       </c>
     </row>
-    <row r="32" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="6">
+        <v>112978</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E32" s="14"/>
+      <c r="F32" s="10">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" s="3">
         <v>118874</v>
       </c>
-      <c r="D32" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="13"/>
-      <c r="F32" s="14">
+      <c r="D33" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E33" s="13"/>
+      <c r="F33" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C34" s="3">
         <v>134629</v>
       </c>
-      <c r="D33" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="14">
+      <c r="D34" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E34" s="13"/>
+      <c r="F34" s="9">
         <v>5.49</v>
       </c>
     </row>
-    <row r="34" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C34" s="11">
+      <c r="C35" s="3">
         <v>157422</v>
       </c>
-      <c r="D34" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="14">
+      <c r="D35" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="13"/>
+      <c r="F35" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="35" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="11">
-        <v>166152</v>
-      </c>
-      <c r="D35" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="14">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="7">
+      <c r="C36" s="3">
+        <v>166152</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="13"/>
+      <c r="F36" s="9">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="3">
         <v>170874</v>
       </c>
-      <c r="D36" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="10">
+      <c r="D37" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="13"/>
+      <c r="F37" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="11">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="3">
         <v>101066</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D38" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="13"/>
+      <c r="F38" s="9">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="14">
-        <v>2.89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C38" s="7">
+      <c r="C39" s="3">
         <v>101063</v>
       </c>
-      <c r="D38" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="9"/>
-      <c r="F38" s="10">
+      <c r="D39" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E39" s="13"/>
+      <c r="F39" s="9">
         <v>3.79</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="11">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40" s="3">
         <v>144940</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="13"/>
+      <c r="F40" s="9">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="14">
-        <v>7.29</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C40" s="11">
+      <c r="C41" s="3">
         <v>219003</v>
       </c>
-      <c r="D40" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="14">
+      <c r="D41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="13"/>
+      <c r="F41" s="9">
         <v>9.19</v>
       </c>
     </row>
-    <row r="41" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C41" s="7">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="3">
         <v>170363</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="9"/>
-      <c r="F41" s="10">
+      <c r="D42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E42" s="13"/>
+      <c r="F42" s="9">
         <v>7.49</v>
       </c>
     </row>
-    <row r="42" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" s="11">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C43" s="3">
         <v>173725</v>
       </c>
-      <c r="D42" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="14">
+      <c r="D43" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="13"/>
+      <c r="F43" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="44" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C44" s="11">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="6">
         <v>104406</v>
       </c>
-      <c r="D44" s="12" t="s">
+      <c r="D45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E45" s="14"/>
+      <c r="F45" s="10">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="E44" s="13"/>
-      <c r="F44" s="14">
-        <v>11.29</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C45" s="11">
+      <c r="C46" s="3">
         <v>104410</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="13"/>
-      <c r="F45" s="14">
+      <c r="D46" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E46" s="13"/>
+      <c r="F46" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C46" s="11">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="3">
         <v>170398</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="14">
+      <c r="D47" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E47" s="13"/>
+      <c r="F47" s="9">
         <v>11.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="11">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="3">
         <v>286325</v>
       </c>
-      <c r="D47" s="12" t="s">
+      <c r="D48" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="13"/>
+      <c r="F48" s="9">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="14">
-        <v>22.99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C48" s="11">
+      <c r="C49" s="3">
         <v>157066</v>
       </c>
-      <c r="D48" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="14">
+      <c r="D49" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E49" s="13"/>
+      <c r="F49" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C49" s="11">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="3">
         <v>247799</v>
       </c>
-      <c r="D49" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="14">
+      <c r="D50" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E50" s="13"/>
+      <c r="F50" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="50" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="7">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="6">
         <v>341231</v>
       </c>
-      <c r="D50" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="10">
+      <c r="D51" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="E51" s="14"/>
+      <c r="F51" s="10">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
-    <row r="51" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C51" s="7">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="C52" s="6">
         <v>324556</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="10">
+      <c r="D52" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E52" s="14"/>
+      <c r="F52" s="10">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C52" s="11">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="3">
         <v>102085</v>
       </c>
-      <c r="D52" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="14">
+      <c r="D53" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E53" s="13"/>
+      <c r="F53" s="9">
         <v>13.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54" s="11">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C55" s="3">
         <v>107943</v>
       </c>
-      <c r="D54" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" s="13"/>
-      <c r="F54" s="14">
+      <c r="D55" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="E55" s="13"/>
+      <c r="F55" s="9">
         <v>12.19</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C55" s="11">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C56" s="3">
         <v>133368</v>
       </c>
-      <c r="D55" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="14">
+      <c r="D56" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E56" s="13"/>
+      <c r="F56" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C56" s="11">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C57" s="3">
         <v>204822</v>
       </c>
-      <c r="D56" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="14">
+      <c r="D57" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E57" s="13"/>
+      <c r="F57" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C57" s="7">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="3">
         <v>100423</v>
       </c>
-      <c r="D57" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="10">
+      <c r="D58" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E58" s="13"/>
+      <c r="F58" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C58" s="11">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C59" s="3">
         <v>122716</v>
       </c>
-      <c r="D58" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="14">
+      <c r="D59" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E59" s="13"/>
+      <c r="F59" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="59" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C59" s="11">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C60" s="3">
         <v>225564</v>
       </c>
-      <c r="D59" s="12" t="s">
+      <c r="D60" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" s="13"/>
+      <c r="F60" s="9">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="14">
+      <c r="C61" s="3">
+        <v>259568</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E61" s="13"/>
+      <c r="F61" s="9">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="3">
+        <v>260718</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E63" s="13"/>
+      <c r="F63" s="9">
+        <v>86.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="3">
+        <v>297599</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="9">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="3">
+        <v>104188</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" s="13"/>
+      <c r="F65" s="9">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="3">
+        <v>200634</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="13"/>
+      <c r="F66" s="9">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C67" s="3">
+        <v>137299</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="E67" s="13"/>
+      <c r="F67" s="9">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C68" s="3">
+        <v>186153</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E68" s="13"/>
+      <c r="F68" s="9">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C69" s="3">
+        <v>170506</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E69" s="13"/>
+      <c r="F69" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C70" s="3">
+        <v>108140</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="9">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C71" s="3">
+        <v>235023</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="9">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C72" s="3">
+        <v>346940</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E72" s="13"/>
+      <c r="F72" s="9">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="60" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C60" s="7">
-        <v>259568</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="10">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C62" s="11">
-        <v>260718</v>
-      </c>
-      <c r="D62" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E62" s="13"/>
-      <c r="F62" s="14">
-        <v>86.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63" s="11">
-        <v>297599</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="14">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C64" s="11">
-        <v>104188</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="14">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C65" s="11">
-        <v>200634</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="14">
-        <v>18.989999999999998</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C66" s="11">
-        <v>137299</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="14">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C67" s="11">
-        <v>186153</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="14">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" s="11">
-        <v>170506</v>
-      </c>
-      <c r="D68" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="14">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C69" s="11">
-        <v>108140</v>
-      </c>
-      <c r="D69" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="14">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C70" s="11">
-        <v>235023</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="14">
+    <row r="73" spans="1:6" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C73" s="3">
+        <v>149627</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E73" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="F73" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="71" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C71" s="11">
-        <v>346940</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="14">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C72" s="11">
-        <v>149627</v>
-      </c>
-      <c r="D72" s="12" t="s">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="E72" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="F72" s="14">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C73" s="11">
+      <c r="C74" s="3">
         <v>216127</v>
       </c>
-      <c r="D73" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="E73" s="13"/>
-      <c r="F73" s="14">
+      <c r="D74" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E74" s="13"/>
+      <c r="F74" s="9">
         <v>3.69</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,19 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC199DD8-8EEB-49AB-90A9-E457C98A8A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585788AE-DB4D-4772-B864-A5B3D1E00098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="113">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,28 +40,25 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>SEGUNDA A QUARTA - OFERTAS 17 A 19/08/26</t>
+    <t>QUINTA A SABADO - OFERTAS 20 A 22/08/26</t>
   </si>
   <si>
     <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
   </si>
   <si>
-    <t>ARROZ KIDELICIA PCT 5KG TIPO 1 BRANCO</t>
-  </si>
-  <si>
-    <t>ARROZ MEU BIJU PCT 5KG TIPO 1 BRANCO</t>
-  </si>
-  <si>
-    <t>ARROZ SANTA FÉ PCT 5KG TIPO 1 BRANCO</t>
+    <t>ARROZ BREJEIRO PCT 5KG TIPO 1 BRANCO</t>
+  </si>
+  <si>
+    <t>ARROZ SELEÇÃO PCT 5KG TIPO 1 BRANCO</t>
   </si>
   <si>
     <t>#01 MERCEARIA - #02 FEIJÕES E LEGUMINOSAS</t>
   </si>
   <si>
-    <t>FEIJÃO CARIOCA KALDINHO 1KG</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FEIJÃO PRETO KICALDO 1KG </t>
+    <t>FEIJÃO CARIOCA BOM DE CALDO 1KG</t>
+  </si>
+  <si>
+    <t>FEIJÃO DE CORDA DONA DE 1KG</t>
   </si>
   <si>
     <t>#01 MERCEARIA - #03 ÓLEOS E GORDURAS</t>
@@ -73,7 +70,7 @@
     <t>#01 MERCEARIA - #04 AÇÚCAR E ADOÇANTES</t>
   </si>
   <si>
-    <t>AÇUCAR ECOÇUCAR 2KG CRISTAL</t>
+    <t>AÇÚCAR TAPAJOS 2KG CRISTAL</t>
   </si>
   <si>
     <t>#02 MERCEARIA - ACHOCOLATADOS E CAFÉ</t>
@@ -82,79 +79,61 @@
     <t>ACHOCOLATADO DANETTE 200ML</t>
   </si>
   <si>
-    <t>CAFE MAMORE 250G TRADICIONAL TORRADO E MOIDO</t>
+    <t>ACHOCOLATADO EM PÓ TODDY 750G</t>
   </si>
   <si>
     <t>CAFÉ MARATA 250G TRADICIONAL</t>
   </si>
   <si>
+    <t>CAFÉ RANCHEIRO 250G TRADICIONAL</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - BISCOITOS E SALGADINHOS</t>
   </si>
   <si>
-    <t>BISCOITO CLUB SOCIAL 144G ORIGINAL</t>
-  </si>
-  <si>
     <t>BISCOITO CREAM CRACKER FORTALEZA 350G</t>
   </si>
   <si>
     <t>BISCOITO ROSQUINHA ADORALLE 600G COCO</t>
   </si>
   <si>
-    <t>BOLACHA QUEBRADOR SUSPIRINHO MINEIRO 250G</t>
+    <t>#02 MERCEARIA - CHOCOLATES E DOCES</t>
+  </si>
+  <si>
+    <t>BOMBOM GAROTO CAIXA 220G SORTIDOS</t>
   </si>
   <si>
     <t>#02 MERCEARIA - CONDIMENTOS E TEMPEROS</t>
   </si>
   <si>
-    <t>AZEITONAS VALE FERTIL 50G SNACK CHILLI</t>
-  </si>
-  <si>
-    <t>AZEITONAS VERDES AMAFIL 580G COM CAROÇO</t>
-  </si>
-  <si>
-    <t>AZEITONAS VERDES VALE FERTIL 150G COM CAROÇO</t>
-  </si>
-  <si>
-    <t>CHAMPIGNON VALE FERTIL 100G FATIADO</t>
-  </si>
-  <si>
-    <t>COGUMELO EM CONSERVA OLE VIDRO 100G</t>
-  </si>
-  <si>
     <t>EXTRATO DE TOMATE ELEFANTE POTE 300G</t>
   </si>
   <si>
-    <t>MOLHO DE TOMATE SABORELLE 300G TRADICIONAL</t>
-  </si>
-  <si>
-    <t>TEMPERO COMPLETO SABOR AMI 1KG COM PIMENTA</t>
-  </si>
-  <si>
-    <t>TEMPERO SABOR AMI 300G SEM PIMENTA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VINAGRE MARATÁ 750ML ALCOOL </t>
-  </si>
-  <si>
-    <t>#02 MERCEARIA - CONGELADOS - MASSAS</t>
-  </si>
-  <si>
-    <t>MASSA PARA LASANHA FORTALEZA 500G COM OVOS</t>
+    <t>EXTRATO DE TOMATE QUERO 1,080KG</t>
+  </si>
+  <si>
+    <t>MAIONESE HELLMANNS 500G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>MOLHO DE TOMATE DEZ 300G TRADICIONAL</t>
+  </si>
+  <si>
+    <t>TEMPERO COMPLETO ARISCO COMPLETO 1KG SEM PIMENTA</t>
+  </si>
+  <si>
+    <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
   </si>
   <si>
     <t>#02 MERCEARIA - CONSERVAS - HORTIFRUTI</t>
   </si>
   <si>
-    <t>MILHO VERDE SOFRUTA LATA 170G</t>
+    <t>MILHO VERDE QUERO LATA 170G</t>
   </si>
   <si>
     <t>#02 MERCEARIA - CONSERVAS - SARDINHAS</t>
   </si>
   <si>
-    <t>ATUM OLE LATA 170G SOLIDO OLEO</t>
-  </si>
-  <si>
-    <t>ATUM RALADO 88 140G NATURAL</t>
+    <t>SARDINHA GOMES DA COSTA 125G TOMATE</t>
   </si>
   <si>
     <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
@@ -163,82 +142,76 @@
     <t>CUSCUZ DE MILHO SABOR DO PARA 500G</t>
   </si>
   <si>
-    <t>CUSCUZ DE MILHO SINHA 500G</t>
-  </si>
-  <si>
-    <t>FARINHA DE MANDIOCA BIJU AMAFIL 500G TORRADA</t>
-  </si>
-  <si>
     <t>FARINHA DE TRIGO MIRELLA 1KG SEM FERMENTO PAPEL</t>
   </si>
   <si>
-    <t>FLOCÃO ARROZ CORINGA 500G</t>
-  </si>
-  <si>
-    <t>FLOCÃO DE MILHO CORINGA 500G SUPER FLOCÃO</t>
-  </si>
-  <si>
-    <t>MASSA PARA TAPIOCA ROCHA 500G PRONTA</t>
+    <t>FLOCÃO DE ARROZ SABOR DO PARA 400G</t>
+  </si>
+  <si>
+    <t>FLOCÃO DE MILHO DONA CLARA 500G</t>
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - DERIVADOS LACTEOS</t>
   </si>
   <si>
-    <t>CREME DE LEITE ITALAC 200G</t>
-  </si>
-  <si>
     <t>CREME DE LEITE PIRACANJUBA 200G</t>
   </si>
   <si>
+    <t>LEITE CONDENSADO PIRACANJUBA 395G</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
   </si>
   <si>
-    <t>LEITE LONGA VIDA ITALAC 1L DESNATADO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LEITE LONGA VIDA ITALAC 1L INTEGRAL ZERO LACTOSE </t>
+    <t>LEITE LONGA VIDA ITALAC 1L SEMI DESNATADO</t>
   </si>
   <si>
     <t>LEITE LONGA VIDA LEITBOM 1L INTEGRAL</t>
   </si>
   <si>
+    <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
+  </si>
+  <si>
+    <t>LEITE EM PÓ CCGL 1KG INTEGRAL</t>
+  </si>
+  <si>
     <t>#02 MERCEARIA - MASSAS</t>
   </si>
   <si>
-    <t xml:space="preserve">MACARRÃO CRISTAL ESPAGUETE 500G INTEGRAL </t>
+    <t>MACARRÃO GALO ESPAGUETE Nº8 VERMELHO 500G</t>
+  </si>
+  <si>
+    <t>MASSA PARA LASANHA CRISTAL 500G</t>
   </si>
   <si>
     <t>#05 BEBIDA - #00 BEBIDAS GASEIFICADAS</t>
   </si>
   <si>
+    <t>GUARANA ANTARTICA 2L DIET</t>
+  </si>
+  <si>
     <t>REFRIGERANTE COCA COLA 2L</t>
   </si>
   <si>
-    <t>REFRIGERANTE GUARANA ANTARCTICA 2L</t>
-  </si>
-  <si>
-    <t>REFRIGERANTE JESUS 2L</t>
+    <t>ÁGUA MINERAL BELAGUA 500ML COM GAS</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
+  </si>
+  <si>
+    <t>ENERGETICO EXTRA POWER 270ML</t>
   </si>
   <si>
     <t>#05 BEBIDA - #01 SUCOS PRONTOS</t>
   </si>
   <si>
-    <t>SUCO AURORA TP 1,5L UVA TINTO</t>
-  </si>
-  <si>
-    <t>SUCO MAGUARY NECTAR 1L CAJU</t>
-  </si>
-  <si>
-    <t>#05 BEBIDA - CERVEJAS</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER LAGER LONG NECK 330ML</t>
+    <t>SUCO PRONTO DAFRUTA 1L CAJU</t>
   </si>
   <si>
     <t>#05 BEBIDA - CERVEJAS CX</t>
   </si>
   <si>
-    <t>CERVEJA ANTARCTICA 15 X 269ML MULTIPACK</t>
+    <t xml:space="preserve">CERVEJA ANTARCTICA PILSEN 15 X 269ML </t>
   </si>
   <si>
     <t>CERVEJA SKOL PILSEN 15 X 269ML</t>
@@ -250,16 +223,34 @@
     <t>CACHAÇA 51 965ML</t>
   </si>
   <si>
+    <t>CACHAÇA SELETA 1L</t>
+  </si>
+  <si>
+    <t>GIN TANQUERAY 750ML LONDON</t>
+  </si>
+  <si>
+    <t>WHISKY BUCHANANS 750ML DELUXE 12 ANOS</t>
+  </si>
+  <si>
+    <t>#05 BEBIDA - FERMENTADOS</t>
+  </si>
+  <si>
+    <t>VINHO PERGOLA 1,47L TINTO SUAVE</t>
+  </si>
+  <si>
     <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
   </si>
   <si>
-    <t>ÁGUA SANITÁRIA YPÊ 2L</t>
+    <t>ÁGUA SANITÁRIA LAVABEM 1L</t>
+  </si>
+  <si>
+    <t>ÁGUA SANITÁRIA QBOA 1L</t>
   </si>
   <si>
     <t>#06 LIMPEZA - AMACIANTES</t>
   </si>
   <si>
-    <t>AMACIANTE DE ROUPAS +FAMILIA 5L ORIGINAL</t>
+    <t>AMACIANTE DE ROUPAS YPÊ 2L DELICADO BRANCO</t>
   </si>
   <si>
     <t>#06 LIMPEZA - DESINFETANTES</t>
@@ -271,85 +262,103 @@
     <t>#06 LIMPEZA - DETERGENTES</t>
   </si>
   <si>
-    <t>DETERGENTE LIQUIDO LIMPOL 500ML</t>
-  </si>
-  <si>
-    <t>#06 LIMPEZA - LIMPA ALUMINIO</t>
-  </si>
-  <si>
-    <t>LIMPA ALUMINIO POLITRIZ 500ML TRADICIONAL</t>
+    <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO YPÊ 500ML CLEAR CARE</t>
+  </si>
+  <si>
+    <t>#06 LIMPEZA - LIMPADORES</t>
+  </si>
+  <si>
+    <t>LIMPADOR PERFUMADO CASAFLOR 1L HARMONY</t>
+  </si>
+  <si>
+    <t>LIMPADOR VEJA MULTI USO 500ML ORIGINAL</t>
   </si>
   <si>
     <t>#06 LIMPEZA - SABÃO</t>
   </si>
   <si>
-    <t>SABÃO EM PÓ BRILHANTE SACHÊ 1,6KG PERFUME PODEROSO</t>
-  </si>
-  <si>
-    <t>SABÃO EM PÓ TIXAN YPÊ SACHÊ 800G MACIEZ</t>
+    <t>SABÃO EM BARRA YPÊ 900G NEUTRO</t>
+  </si>
+  <si>
+    <t>SABÃO EM PÓ TIXAN YPÊ CAIXA 1,6KG MACIEZ</t>
+  </si>
+  <si>
+    <t>#06 LIMPEZA - SODAS</t>
+  </si>
+  <si>
+    <t>SODA CAUSTICA SOL 1KG</t>
   </si>
   <si>
     <t>#07 HIGIENE PESSOAL - CABELOS</t>
   </si>
   <si>
-    <t>KIT SHAMPOO E CONDICIONADOR HASKELL 1KIT CAVALO FORTE</t>
-  </si>
-  <si>
-    <t>KIT SHAMPOO E CONDICIONADOR TURMA DA XUXINHA BARUEL 1KIT INFANTIL</t>
-  </si>
-  <si>
-    <t>SHAMPOO LOREAL ELSEVE 200ML COLOR VIVE</t>
-  </si>
-  <si>
-    <t>XAMPU TURMA DA XUXINHA 400ML SUAVE</t>
+    <t>CREME DE TRATAMENTO ORIGEM 1KG CACHOS CONTROLADOS</t>
   </si>
   <si>
     <t>#07 HIGIENE PESSOAL - DESODORANTE</t>
   </si>
   <si>
-    <t>DESODORANTE TABU AEROSOL 150ML LINDA</t>
-  </si>
-  <si>
-    <t>#07 HIGIENE PESSOAL - HIGIENE</t>
-  </si>
-  <si>
-    <t>ALGODÃO COTTONBABY HIDROFILO ROLO 25G</t>
-  </si>
-  <si>
-    <t>#07 HIGIENE PESSOAL - HIGIENE BUCAL</t>
-  </si>
-  <si>
-    <t>CREME DENTAL ORAL B 70G ANTI CARIES</t>
-  </si>
-  <si>
-    <t>#07 HIGIENE PESSOAL - INTIMA</t>
-  </si>
-  <si>
-    <t>ABSORVENTE INTIMUS GEL 8 X 1 1PTC TRIPLA PROTEÇÃO COM ABAS SECA</t>
-  </si>
-  <si>
-    <t>#07 HIGIENE PESSOAL - MASCULINO</t>
-  </si>
-  <si>
-    <t>APARELHO PARA BARBEAR GILLETTE ULTRA GRIP</t>
+    <t>DESODORANTE BOZZANO AEROSOL 150ML</t>
+  </si>
+  <si>
+    <t>DESODORANTE BOZZANO AEROSOL 90G</t>
+  </si>
+  <si>
+    <t>LOÇÃO HIDRATANTE PAIXÃO 200ML</t>
+  </si>
+  <si>
+    <t>LOÇÃO HIDRATANTE PAIXÃO 200ML FRANBOESA E HIBISCO</t>
   </si>
   <si>
     <t>#07 HIGIENE PESSOAL - PAPEL HIGIENICO</t>
   </si>
   <si>
-    <t>PAPEL HIGIENICO SUBLIME FOLHA DUPLA 12 X 30M PROMOCIONAL</t>
+    <t>PAPEL HIGIENICO NOBLE 6 X 20M FOLHA DUPLA</t>
   </si>
   <si>
     <t>#07 HIGIENE PESSOAL - SABONETE</t>
   </si>
   <si>
-    <t>SABONETE FRANCIS 90G</t>
-  </si>
-  <si>
-    <t>ROMA E PIMENTA ROSA, VERBENA DA SICILIA</t>
-  </si>
-  <si>
-    <t>SABONETE FRANCIS 90G CLASSICO PRETO</t>
+    <t>SABONETE PALMOLIVE 150G</t>
+  </si>
+  <si>
+    <t>SEÇÃO NÃO ESPECIFICADA</t>
+  </si>
+  <si>
+    <t>AZEITONA RIVOLI 120GR FATIADA SACHE DOYP</t>
+  </si>
+  <si>
+    <t>CD MONANGE 325ML RESTAURA QUE GOSTO</t>
+  </si>
+  <si>
+    <t>COPO DESC MARATA BCO COMUM 100X180ML</t>
+  </si>
+  <si>
+    <t>COPO MUNICH NADIR 200ML 7109</t>
+  </si>
+  <si>
+    <t>FARINHA DE MANDIOCA SAFRA 1KG FINA AMARE</t>
+  </si>
+  <si>
+    <t>PAPEL TOALHA KITCHEN 120FLS</t>
+  </si>
+  <si>
+    <t>PETA SABOR QUEIJO PIGNATTA 100G</t>
+  </si>
+  <si>
+    <t>PETA TEMPERADA PIGNATTA 100G</t>
+  </si>
+  <si>
+    <t>POLVILHO SAFRA DOCE 1KG PEROLA</t>
+  </si>
+  <si>
+    <t>SUCO UVA INTEGRAL JOTA PE 1,5L TINT/INTE</t>
+  </si>
+  <si>
+    <t>VODKA ABSOLUT 750ML TRAD</t>
   </si>
 </sst>
 </file>
@@ -359,7 +368,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -395,33 +404,8 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b/>
-      <sz val="7"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="8"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -432,12 +416,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF45A045"/>
-        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -468,7 +446,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -482,13 +460,7 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -497,25 +469,7 @@
     <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -821,15 +775,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -845,10 +799,10 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
@@ -860,14 +814,14 @@
         <v>7</v>
       </c>
       <c r="C2" s="3">
-        <v>229173</v>
+        <v>100038</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="13"/>
-      <c r="F2" s="9">
-        <v>19.989999999999998</v>
+      <c r="E2" s="5"/>
+      <c r="F2" s="7">
+        <v>25.99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -878,14 +832,14 @@
         <v>7</v>
       </c>
       <c r="C3" s="3">
-        <v>141640</v>
+        <v>301961</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="13"/>
-      <c r="F3" s="9">
-        <v>24.99</v>
+      <c r="E3" s="5"/>
+      <c r="F3" s="7">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -893,17 +847,17 @@
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="3">
-        <v>199440</v>
+        <v>274850</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="9">
-        <v>18.989999999999998</v>
+        <v>11</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -911,17 +865,17 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="3">
-        <v>327443</v>
+        <v>183364</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="13"/>
-      <c r="F5" s="9">
-        <v>9.99</v>
+      <c r="E5" s="5"/>
+      <c r="F5" s="7">
+        <v>7.59</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -929,53 +883,53 @@
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="3">
-        <v>140665</v>
+        <v>106680</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" s="13"/>
-      <c r="F6" s="9">
-        <v>8.49</v>
+        <v>14</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="7">
+        <v>8.69</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="6">
-        <v>106680</v>
-      </c>
-      <c r="D7" s="7" t="s">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="14"/>
-      <c r="F7" s="10">
+      <c r="C7" s="3">
+        <v>344096</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="7">
         <v>7.99</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="3">
-        <v>345404</v>
-      </c>
-      <c r="D8" s="4" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="9">
-        <v>5.99</v>
+      <c r="C9" s="3">
+        <v>104679</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="7">
+        <v>3.19</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -983,17 +937,17 @@
         <v>6</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="3">
-        <v>104679</v>
+        <v>255232</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="9">
-        <v>3.19</v>
+      <c r="E10" s="5"/>
+      <c r="F10" s="7">
+        <v>20.99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1001,35 +955,35 @@
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="3">
-        <v>344310</v>
+        <v>101137</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="13"/>
-      <c r="F11" s="9">
-        <v>12.99</v>
+      <c r="E11" s="5"/>
+      <c r="F11" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="6">
-        <v>101137</v>
-      </c>
-      <c r="D12" s="7" t="s">
+      <c r="A12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="3">
+        <v>174298</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="14"/>
-      <c r="F12" s="10">
-        <v>13.99</v>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1040,14 +994,14 @@
         <v>22</v>
       </c>
       <c r="C13" s="3">
-        <v>110372</v>
+        <v>261728</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="9">
-        <v>6.49</v>
+      <c r="E13" s="5"/>
+      <c r="F13" s="7">
+        <v>7.49</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1058,14 +1012,14 @@
         <v>22</v>
       </c>
       <c r="C14" s="3">
-        <v>261728</v>
+        <v>199869</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="9">
-        <v>7.49</v>
+      <c r="E14" s="5"/>
+      <c r="F14" s="7">
+        <v>8.2899999999999991</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1073,17 +1027,17 @@
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3">
-        <v>199869</v>
+        <v>341362</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="9">
-        <v>8.49</v>
+        <v>26</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1091,17 +1045,17 @@
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C16" s="3">
-        <v>263132</v>
+        <v>273714</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="9">
-        <v>10.99</v>
+        <v>28</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="7">
+        <v>9.19</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1112,14 +1066,14 @@
         <v>27</v>
       </c>
       <c r="C17" s="3">
-        <v>280720</v>
+        <v>110043</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="9">
-        <v>5.39</v>
+        <v>29</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="7">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1130,14 +1084,14 @@
         <v>27</v>
       </c>
       <c r="C18" s="3">
-        <v>327574</v>
+        <v>101728</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="9">
-        <v>21.99</v>
+        <v>30</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1148,14 +1102,14 @@
         <v>27</v>
       </c>
       <c r="C19" s="3">
-        <v>253531</v>
+        <v>244444</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E19" s="13"/>
-      <c r="F19" s="9">
-        <v>5.99</v>
+        <v>31</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="7">
+        <v>1.89</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -1166,14 +1120,14 @@
         <v>27</v>
       </c>
       <c r="C20" s="3">
-        <v>343468</v>
+        <v>108518</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E20" s="13"/>
-      <c r="F20" s="9">
-        <v>7.99</v>
+        <v>32</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="7">
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1184,14 +1138,14 @@
         <v>27</v>
       </c>
       <c r="C21" s="3">
-        <v>147187</v>
+        <v>106960</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="13"/>
-      <c r="F21" s="9">
-        <v>9.99</v>
+        <v>33</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1199,17 +1153,17 @@
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C22" s="3">
-        <v>273714</v>
+        <v>107640</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E22" s="13"/>
-      <c r="F22" s="9">
-        <v>8.99</v>
+        <v>35</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1217,17 +1171,17 @@
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C23" s="3">
-        <v>287073</v>
+        <v>100705</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E23" s="13"/>
-      <c r="F23" s="9">
-        <v>2.29</v>
+        <v>37</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1235,17 +1189,17 @@
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C24" s="3">
-        <v>100872</v>
+        <v>262643</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E24" s="13"/>
-      <c r="F24" s="9">
-        <v>17.989999999999998</v>
+        <v>39</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="7">
+        <v>2.59</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1253,16 +1207,16 @@
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C25" s="3">
-        <v>109390</v>
+        <v>134629</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E25" s="13"/>
-      <c r="F25" s="9">
+        <v>40</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="7">
         <v>5.99</v>
       </c>
     </row>
@@ -1271,17 +1225,17 @@
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C26" s="3">
-        <v>113543</v>
+        <v>286303</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E26" s="13"/>
-      <c r="F26" s="9">
-        <v>3.99</v>
+        <v>41</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="7">
+        <v>2.69</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1292,14 +1246,14 @@
         <v>38</v>
       </c>
       <c r="C27" s="3">
-        <v>106781</v>
+        <v>117532</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E27" s="13"/>
-      <c r="F27" s="9">
-        <v>12.99</v>
+        <v>42</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="7">
+        <v>2.19</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1307,17 +1261,17 @@
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C28" s="3">
-        <v>234316</v>
+        <v>101063</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E28" s="13"/>
-      <c r="F28" s="9">
-        <v>4.99</v>
+        <v>44</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="7">
+        <v>3.69</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1325,17 +1279,17 @@
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C29" s="3">
-        <v>207321</v>
+        <v>101083</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E29" s="13"/>
-      <c r="F29" s="9">
-        <v>15.49</v>
+        <v>45</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="7">
+        <v>7.69</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1343,17 +1297,17 @@
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C30" s="3">
-        <v>301367</v>
+        <v>183340</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E30" s="13"/>
-      <c r="F30" s="9">
-        <v>7.99</v>
+        <v>47</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="7">
+        <v>7.19</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,35 +1315,35 @@
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C31" s="3">
-        <v>262643</v>
+        <v>170363</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E31" s="13"/>
-      <c r="F31" s="9">
-        <v>2.59</v>
+        <v>48</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="7">
+        <v>7.89</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C32" s="6">
-        <v>112978</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" s="14"/>
-      <c r="F32" s="10">
-        <v>2.79</v>
+      <c r="A32" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="3">
+        <v>106922</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="7">
+        <v>39.99</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1397,17 +1351,17 @@
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C33" s="3">
-        <v>118874</v>
+        <v>131884</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="9">
-        <v>5.99</v>
+        <v>52</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="7">
+        <v>4.29</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,35 +1369,17 @@
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C34" s="3">
-        <v>134629</v>
+        <v>108414</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E34" s="13"/>
-      <c r="F34" s="9">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C35" s="3">
-        <v>157422</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="9">
-        <v>5.99</v>
+        <v>53</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="7">
+        <v>12.99</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1451,17 +1387,17 @@
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C36" s="3">
-        <v>166152</v>
+        <v>104412</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="13"/>
-      <c r="F36" s="9">
-        <v>3.49</v>
+        <v>55</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="7">
+        <v>8.49</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1469,17 +1405,17 @@
         <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C37" s="3">
-        <v>170874</v>
+        <v>104406</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="13"/>
-      <c r="F37" s="9">
-        <v>6.99</v>
+        <v>56</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1487,17 +1423,17 @@
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C38" s="3">
-        <v>101066</v>
+        <v>150263</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E38" s="13"/>
-      <c r="F38" s="9">
-        <v>2.89</v>
+        <v>57</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="7">
+        <v>1.99</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1505,17 +1441,17 @@
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C39" s="3">
-        <v>101063</v>
+        <v>102287</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E39" s="13"/>
-      <c r="F39" s="9">
-        <v>3.79</v>
+        <v>59</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="7">
+        <v>4.99</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1523,17 +1459,17 @@
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C40" s="3">
-        <v>144940</v>
+        <v>102149</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E40" s="13"/>
-      <c r="F40" s="9">
-        <v>7.29</v>
+        <v>61</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="7">
+        <v>5.99</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1541,17 +1477,17 @@
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C41" s="3">
-        <v>219003</v>
+        <v>168712</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="13"/>
-      <c r="F41" s="9">
-        <v>9.19</v>
+        <v>63</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="7">
+        <v>3.39</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1559,17 +1495,17 @@
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="C42" s="3">
-        <v>170363</v>
+        <v>324556</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E42" s="13"/>
-      <c r="F42" s="9">
-        <v>7.49</v>
+        <v>64</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="7">
+        <v>3.09</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1577,35 +1513,53 @@
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C43" s="3">
-        <v>173725</v>
+        <v>102085</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="E43" s="13"/>
-      <c r="F43" s="9">
-        <v>5.99</v>
+        <v>66</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="7">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="3">
+        <v>145655</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="7">
+        <v>99.99</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C45" s="6">
-        <v>104406</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E45" s="14"/>
-      <c r="F45" s="10">
-        <v>10.99</v>
+      <c r="A45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C45" s="3">
+        <v>206930</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="7">
+        <v>179.99</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1613,17 +1567,17 @@
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C46" s="3">
-        <v>104410</v>
+        <v>262730</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E46" s="13"/>
-      <c r="F46" s="9">
-        <v>9.99</v>
+        <v>69</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="7">
+        <v>239.99</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1631,35 +1585,17 @@
         <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C47" s="3">
-        <v>170398</v>
+        <v>250236</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E47" s="13"/>
-      <c r="F47" s="9">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C48" s="3">
-        <v>286325</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E48" s="13"/>
-      <c r="F48" s="9">
-        <v>22.99</v>
+        <v>71</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="7">
+        <v>42.99</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1667,17 +1603,17 @@
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C49" s="3">
-        <v>157066</v>
+        <v>207638</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E49" s="13"/>
-      <c r="F49" s="9">
-        <v>5.99</v>
+        <v>73</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="7">
+        <v>4.1900000000000004</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1685,55 +1621,53 @@
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C50" s="3">
-        <v>247799</v>
+        <v>100426</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E50" s="13"/>
-      <c r="F50" s="9">
-        <v>6.49</v>
+        <v>74</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="7">
+        <v>5.89</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="6">
-        <v>341231</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="E51" s="14"/>
-      <c r="F51" s="10">
-        <f>15*3.19</f>
-        <v>47.85</v>
+      <c r="A51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="3">
+        <v>107413</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="7">
+        <v>12.99</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C52" s="6">
-        <v>324556</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E52" s="14"/>
-      <c r="F52" s="10">
-        <f>15*2.99</f>
-        <v>44.85</v>
+      <c r="A52" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" s="3">
+        <v>204822</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="7">
+        <v>7.99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,17 +1675,35 @@
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C53" s="3">
-        <v>102085</v>
+        <v>100391</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E53" s="13"/>
-      <c r="F53" s="9">
-        <v>13.99</v>
+        <v>80</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="7">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54" s="3">
+        <v>100392</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="7">
+        <v>3.19</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1759,17 +1711,17 @@
         <v>6</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C55" s="3">
-        <v>107943</v>
+        <v>173946</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E55" s="13"/>
-      <c r="F55" s="9">
-        <v>12.19</v>
+        <v>83</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="7">
+        <v>9.49</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1777,17 +1729,17 @@
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C56" s="3">
-        <v>133368</v>
+        <v>107645</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="9">
-        <v>20.99</v>
+        <v>84</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="7">
+        <v>5.29</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,17 +1747,17 @@
         <v>6</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C57" s="3">
-        <v>204822</v>
+        <v>257710</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E57" s="13"/>
-      <c r="F57" s="9">
-        <v>7.99</v>
+        <v>86</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1813,17 +1765,17 @@
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C58" s="3">
-        <v>100423</v>
+        <v>260547</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="13"/>
-      <c r="F58" s="9">
-        <v>2.99</v>
+        <v>87</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="7">
+        <v>22.99</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,35 +1783,17 @@
         <v>6</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C59" s="3">
-        <v>122716</v>
+        <v>100373</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="E59" s="13"/>
-      <c r="F59" s="9">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C60" s="3">
-        <v>225564</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E60" s="13"/>
-      <c r="F60" s="9">
-        <v>19.989999999999998</v>
+        <v>89</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="7">
+        <v>26.39</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1867,17 +1801,35 @@
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C61" s="3">
-        <v>259568</v>
+        <v>125913</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E61" s="13"/>
-      <c r="F61" s="9">
-        <v>11.99</v>
+        <v>91</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="7">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C62" s="3">
+        <v>142889</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1885,17 +1837,17 @@
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C63" s="3">
-        <v>260718</v>
+        <v>246099</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E63" s="13"/>
-      <c r="F63" s="9">
-        <v>86.99</v>
+        <v>94</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="7">
+        <v>10.99</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1903,17 +1855,17 @@
         <v>6</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C64" s="3">
-        <v>297599</v>
+        <v>264234</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" s="13"/>
-      <c r="F64" s="9">
-        <v>23.99</v>
+        <v>95</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="7">
+        <v>16.989999999999998</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1921,17 +1873,17 @@
         <v>6</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C65" s="3">
-        <v>104188</v>
+        <v>197581</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E65" s="13"/>
-      <c r="F65" s="9">
-        <v>12.99</v>
+        <v>96</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="7">
+        <v>20.99</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1939,17 +1891,17 @@
         <v>6</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C66" s="3">
-        <v>200634</v>
+        <v>346964</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E66" s="13"/>
-      <c r="F66" s="9">
-        <v>18.989999999999998</v>
+        <v>98</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="7">
+        <v>14.99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,35 +1909,17 @@
         <v>6</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C67" s="3">
-        <v>137299</v>
+        <v>144261</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E67" s="13"/>
-      <c r="F67" s="9">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C68" s="3">
-        <v>186153</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="9">
-        <v>2.99</v>
+        <v>100</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="7">
+        <v>3.99</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1993,17 +1927,17 @@
         <v>6</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C69" s="3">
-        <v>170506</v>
+        <v>345990</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E69" s="13"/>
-      <c r="F69" s="9">
-        <v>4.99</v>
+        <v>102</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="7">
+        <v>5.99</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2011,17 +1945,17 @@
         <v>6</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C70" s="3">
-        <v>108140</v>
+        <v>241292</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="9">
-        <v>4.99</v>
+        <v>103</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="7">
+        <v>11.99</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2029,17 +1963,17 @@
         <v>6</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C71" s="3">
-        <v>235023</v>
+        <v>146084</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E71" s="13"/>
-      <c r="F71" s="9">
-        <v>3.99</v>
+        <v>104</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="7">
+        <v>6.99</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -2047,37 +1981,35 @@
         <v>6</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C72" s="3">
-        <v>346940</v>
+        <v>117689</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E72" s="13"/>
-      <c r="F72" s="9">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" ht="33.75" x14ac:dyDescent="0.25">
+      <c r="E72" s="5"/>
+      <c r="F72" s="7">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B73" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C73" s="3">
+        <v>262011</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C73" s="3">
-        <v>149627</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E73" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="F73" s="9">
-        <v>3.99</v>
+      <c r="E73" s="5"/>
+      <c r="F73" s="7">
+        <v>7.49</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2085,24 +2017,114 @@
         <v>6</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C74" s="3">
-        <v>216127</v>
+        <v>116222</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C75" s="3">
+        <v>207770</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C76" s="3">
+        <v>207771</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E74" s="13"/>
-      <c r="F74" s="9">
-        <v>3.69</v>
+      <c r="E76" s="5"/>
+      <c r="F76" s="7">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" s="3">
+        <v>334256</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="7">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C78" s="3">
+        <v>102233</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="7">
+        <v>48.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="3">
+        <v>179089</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="7">
+        <v>128.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="78" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="96" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C'&amp;P - &amp;N</oddHeader>
   </headerFooter>
 </worksheet>
 </file>
--- a/giro_da_praça_ofertas - ARRASADORAS.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16130B40-DBA5-4EF4-9BC2-A1570FECFE45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2BF02CB-743C-4395-9025-E30C119064E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="21480" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ofertas Finais" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="103">
   <si>
     <t>NOME_PROMOÇÃO</t>
   </si>
@@ -40,7 +40,7 @@
     <t>PROMOÇÃO</t>
   </si>
   <si>
-    <t>QUINTA A SABADO - OFERTAS 27 A 29/08/26 MATRIZ</t>
+    <t>QUINTA E SEXTA - OFERTAS 27 E 28/08/26 MATRIZ</t>
   </si>
   <si>
     <t>#01 MERCEARIA - #01 CEREAIS E GRÃOS</t>
@@ -163,6 +163,9 @@
     <t>#02 MERCEARIA - FARINHAS E DERIVADOS</t>
   </si>
   <si>
+    <t>CUSCUZ DE MILHO MARATA 500G</t>
+  </si>
+  <si>
     <t>CUSCUZ DE MILHO SABOR DO PARA 500G</t>
   </si>
   <si>
@@ -172,6 +175,9 @@
     <t>FARINHA DE TRIGO DONA BENTA 1KG COM FERMENTO</t>
   </si>
   <si>
+    <t>FLOCÃO DE ARROZ URBANO 500G</t>
+  </si>
+  <si>
     <t>FLOCÃO DE MILHO AMAFIL 500G</t>
   </si>
   <si>
@@ -226,6 +232,9 @@
     <t>#05 BEBIDA - #00 ENERGÉTICOS</t>
   </si>
   <si>
+    <t>ENERGETICO EXTRA POWER 2L TROPICAL</t>
+  </si>
+  <si>
     <t>ENERGETICO RED BULL 250ML TRADICIONAL</t>
   </si>
   <si>
@@ -256,6 +265,12 @@
     <t>VINHO GALIOTTO 1L TINTO SUAVE</t>
   </si>
   <si>
+    <t>#06 LIMPEZA - ALCOOL</t>
+  </si>
+  <si>
+    <t>ALCOOL LIQUIDO SOL 46° 500ML</t>
+  </si>
+  <si>
     <t>#06 LIMPEZA - ALVEJANTES E ÁGUA SANITÁRIA</t>
   </si>
   <si>
@@ -286,6 +301,15 @@
     <t>DETERGENTE LIQUIDO YPÊ 500ML</t>
   </si>
   <si>
+    <t>#06 LIMPEZA - PAPEIS TOALHA</t>
+  </si>
+  <si>
+    <t>GUARDANAPO VALOR 33X30CM 50 FOLHAS</t>
+  </si>
+  <si>
+    <t>PAPEL TOALHA SOCIAL CLEAN 2X1 BRANCO</t>
+  </si>
+  <si>
     <t>#06 LIMPEZA - SABÃO</t>
   </si>
   <si>
@@ -295,31 +319,16 @@
     <t>SABÃO EM PÓ TIXAN YPÊ SACHÊ 800G PRIMAVERA</t>
   </si>
   <si>
-    <t>SEÇÃO NÃO ESPECIFICADA</t>
-  </si>
-  <si>
-    <t>ALCOOL SOL 46° 500ML LIQUIDO</t>
-  </si>
-  <si>
-    <t>COPO DESC CRISTALCOPO TRANSP 180ML</t>
-  </si>
-  <si>
-    <t>COPO LIGHT S NADIR 260 ML</t>
-  </si>
-  <si>
-    <t>CUSCUZ MILHO MARATA SCH 500G</t>
-  </si>
-  <si>
-    <t>ENERGETICO EXTRA POWER 2L TROPICAL</t>
-  </si>
-  <si>
-    <t>FLOCAO DE ARROZ 500GR URBANO</t>
-  </si>
-  <si>
-    <t>GUARDANAPO VALOR 33X30CM 50UN</t>
-  </si>
-  <si>
-    <t>PAPEL TOALHA SOCIAL CLEAN 2X1 BRANCO</t>
+    <t>#08 BAZAR - DESCARTÁVEIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPOS DESCARTAVEIS CRISTALCOPO 180ML TRANSPARENTES </t>
+  </si>
+  <si>
+    <t>#08 BAZAR - PANELAS E UTENSÍLIOS DE COZINHA</t>
+  </si>
+  <si>
+    <t>COPO NADIR 260ML LIGHT</t>
   </si>
 </sst>
 </file>
@@ -329,7 +338,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -349,24 +358,47 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="16"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -377,6 +409,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -407,7 +445,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -415,22 +453,47 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -737,1215 +800,1215 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="43.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="44.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="80" style="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="6">
         <v>343313</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="7">
+      <c r="E2" s="15"/>
+      <c r="F2" s="8">
         <v>24.96</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>199440</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="7">
+      <c r="E3" s="15"/>
+      <c r="F3" s="8">
         <v>19.989999999999998</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="9">
         <v>279573</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="7">
-        <v>10.49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E4" s="16"/>
+      <c r="F4" s="11">
+        <v>10.29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>254462</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="7">
+      <c r="E5" s="15"/>
+      <c r="F5" s="8">
         <v>7.69</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="9">
         <v>106680</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="7">
-        <v>8.69</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="E6" s="16"/>
+      <c r="F6" s="11">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="9">
         <v>345404</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E7" s="16"/>
+      <c r="F7" s="11">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="6">
         <v>104679</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="7">
+      <c r="E9" s="15"/>
+      <c r="F9" s="8">
         <v>3.29</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="9">
         <v>255232</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="7">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="2" t="s">
+      <c r="E10" s="16"/>
+      <c r="F10" s="11">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="9">
         <v>174298</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="7">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="16"/>
+      <c r="F11" s="11">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="6">
         <v>249399</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="7">
+      <c r="E12" s="15"/>
+      <c r="F12" s="8">
         <v>8.49</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="3">
+      <c r="C13" s="6">
         <v>267812</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="7">
+      <c r="E13" s="15"/>
+      <c r="F13" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="6">
         <v>257157</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="7">
+      <c r="E14" s="15"/>
+      <c r="F14" s="8">
         <v>8.49</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="6">
         <v>207770</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="8">
         <v>10.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="9">
         <v>341362</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="7">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E16" s="16"/>
+      <c r="F16" s="11">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="6">
         <v>295002</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="7">
+      <c r="E17" s="15"/>
+      <c r="F17" s="8">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="6">
         <v>132657</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="7">
+      <c r="E18" s="15"/>
+      <c r="F18" s="8">
         <v>49.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="3">
+      <c r="C19" s="6">
         <v>327574</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="7">
+      <c r="E19" s="15"/>
+      <c r="F19" s="8">
         <v>22.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="6">
         <v>205267</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="7">
+      <c r="E20" s="15"/>
+      <c r="F20" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="6">
         <v>343468</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="7">
+      <c r="E21" s="15"/>
+      <c r="F21" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="6">
         <v>273714</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="7">
+      <c r="E22" s="15"/>
+      <c r="F22" s="8">
         <v>9.2899999999999991</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="3">
+      <c r="C23" s="6">
         <v>336565</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="7">
+      <c r="E23" s="15"/>
+      <c r="F23" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="6">
         <v>101728</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="7">
+      <c r="E24" s="15"/>
+      <c r="F24" s="8">
         <v>11.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="3">
+      <c r="C25" s="6">
         <v>287073</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="7">
+      <c r="E25" s="15"/>
+      <c r="F25" s="8">
         <v>2.29</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C26" s="6">
         <v>111010</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="7">
+      <c r="E26" s="15"/>
+      <c r="F26" s="8">
         <v>14.49</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="3">
+      <c r="C27" s="6">
         <v>141367</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="7">
+      <c r="E27" s="15"/>
+      <c r="F27" s="8">
         <v>3.49</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C28" s="6">
         <v>107640</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="7">
+      <c r="E28" s="15"/>
+      <c r="F28" s="8">
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C29" s="6">
         <v>207321</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="7">
+      <c r="E29" s="15"/>
+      <c r="F29" s="8">
         <v>15.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="3">
+      <c r="C30" s="6">
         <v>116996</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="7">
+      <c r="E30" s="15"/>
+      <c r="F30" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C31" s="3">
-        <v>262643</v>
-      </c>
-      <c r="D31" s="4" t="s">
+      <c r="C31" s="6">
+        <v>139778</v>
+      </c>
+      <c r="D31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="7">
-        <v>2.59</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E31" s="15"/>
+      <c r="F31" s="8">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C32" s="3">
-        <v>109159</v>
-      </c>
-      <c r="D32" s="4" t="s">
+      <c r="C32" s="6">
+        <v>262643</v>
+      </c>
+      <c r="D32" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E32" s="15"/>
+      <c r="F32" s="8">
+        <v>2.59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C33" s="3">
-        <v>107361</v>
-      </c>
-      <c r="D33" s="4" t="s">
+      <c r="C33" s="6">
+        <v>109159</v>
+      </c>
+      <c r="D33" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="7">
-        <v>5.69</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E33" s="15"/>
+      <c r="F33" s="8">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="3">
-        <v>255841</v>
-      </c>
-      <c r="D34" s="4" t="s">
+      <c r="C34" s="6">
+        <v>107361</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="7">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E34" s="15"/>
+      <c r="F34" s="8">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="3">
-        <v>313827</v>
-      </c>
-      <c r="D35" s="4" t="s">
+      <c r="C35" s="6">
+        <v>320648</v>
+      </c>
+      <c r="D35" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E35" s="15"/>
+      <c r="F35" s="8">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="3">
+      <c r="C36" s="6">
+        <v>255841</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="15"/>
+      <c r="F36" s="8">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="6">
+        <v>313827</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E37" s="15"/>
+      <c r="F37" s="8">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="6">
         <v>334256</v>
       </c>
-      <c r="D36" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="7">
+      <c r="D38" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="15"/>
+      <c r="F38" s="8">
         <v>9.49</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" s="3">
+    <row r="39" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="6">
         <v>101063</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="7">
+      <c r="D39" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E39" s="15"/>
+      <c r="F39" s="8">
         <v>3.69</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C38" s="3">
+    <row r="40" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C40" s="6">
         <v>101083</v>
       </c>
-      <c r="D38" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="7">
+      <c r="D40" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E40" s="15"/>
+      <c r="F40" s="8">
         <v>7.69</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C39" s="3">
+    <row r="41" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="6">
         <v>183340</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="7">
+      <c r="D41" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E41" s="15"/>
+      <c r="F41" s="8">
         <v>7.29</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="3">
+    <row r="42" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="9">
         <v>170363</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="7">
-        <v>7.89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C41" s="3">
-        <v>307145</v>
-      </c>
-      <c r="D41" s="4" t="s">
+      <c r="D42" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="7">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C42" s="3">
-        <v>131884</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="7">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E42" s="16"/>
+      <c r="F42" s="11">
+        <v>7.59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C43" s="6">
+        <v>307145</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="15"/>
+      <c r="F43" s="8">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C44" s="6">
+        <v>131884</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" s="15"/>
+      <c r="F44" s="8">
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45" s="6">
         <v>108414</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="7">
+      <c r="D45" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" s="15"/>
+      <c r="F45" s="8">
         <v>12.99</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C45" s="3">
+    <row r="47" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C47" s="6">
         <v>104406</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="7">
+      <c r="D47" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E47" s="15"/>
+      <c r="F47" s="8">
         <v>11.49</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C46" s="3">
+    <row r="48" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C48" s="6">
         <v>104410</v>
       </c>
-      <c r="D46" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="7">
+      <c r="D48" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="E48" s="15"/>
+      <c r="F48" s="8">
         <v>9.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="3">
+    <row r="49" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="6">
+        <v>286959</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E49" s="15"/>
+      <c r="F49" s="8">
+        <v>14.39</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C50" s="6">
         <v>102282</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="7">
+      <c r="D50" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="E50" s="15"/>
+      <c r="F50" s="8">
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" s="3">
+    <row r="51" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C51" s="6">
         <v>264452</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="7">
+      <c r="D51" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="15"/>
+      <c r="F51" s="8">
         <v>4.99</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C49" s="3">
+    <row r="52" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C52" s="9">
         <v>341231</v>
       </c>
-      <c r="D49" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="7">
+      <c r="D52" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="11">
         <f>15*3.19</f>
         <v>47.85</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C50" s="3">
+    <row r="53" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C53" s="9">
         <v>324556</v>
       </c>
-      <c r="D50" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="7">
+      <c r="D53" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E53" s="16"/>
+      <c r="F53" s="11">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="3">
+    <row r="54" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C54" s="6">
         <v>102085</v>
       </c>
-      <c r="D51" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="7">
+      <c r="D54" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E54" s="15"/>
+      <c r="F54" s="8">
         <v>13.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="3">
+    <row r="55" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55" s="6">
         <v>102036</v>
       </c>
-      <c r="D52" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="7">
+      <c r="D55" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E55" s="15"/>
+      <c r="F55" s="8">
         <v>29.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C54" s="3">
-        <v>207640</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="E54" s="5"/>
-      <c r="F54" s="7">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C55" s="3">
-        <v>100426</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="E55" s="5"/>
-      <c r="F55" s="7">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B56" s="2" t="s">
+    <row r="57" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C56" s="3">
-        <v>107394</v>
-      </c>
-      <c r="D56" s="4" t="s">
+      <c r="C57" s="6">
+        <v>297817</v>
+      </c>
+      <c r="D57" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="E56" s="5"/>
-      <c r="F56" s="7">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C57" s="3">
-        <v>247502</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E57" s="5"/>
-      <c r="F57" s="7">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E57" s="15"/>
+      <c r="F57" s="8">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C58" s="3">
-        <v>204822</v>
-      </c>
-      <c r="D58" s="4" t="s">
+      <c r="C58" s="6">
+        <v>207640</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E58" s="15"/>
+      <c r="F58" s="8">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C59" s="6">
+        <v>100426</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E58" s="5"/>
-      <c r="F58" s="7">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="E59" s="15"/>
+      <c r="F59" s="8">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C59" s="3">
-        <v>100391</v>
-      </c>
-      <c r="D59" s="4" t="s">
+      <c r="C60" s="6">
+        <v>107394</v>
+      </c>
+      <c r="D60" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="E59" s="5"/>
-      <c r="F59" s="7">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C60" s="3">
-        <v>257710</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="E60" s="5"/>
-      <c r="F60" s="7">
-        <v>16.989999999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E60" s="15"/>
+      <c r="F60" s="8">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="3">
-        <v>261174</v>
-      </c>
-      <c r="D61" s="4" t="s">
+      <c r="C61" s="6">
+        <v>247502</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E61" s="15"/>
+      <c r="F61" s="8">
+        <v>19.989999999999998</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C62" s="6">
+        <v>204822</v>
+      </c>
+      <c r="D62" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E61" s="5"/>
-      <c r="F61" s="7">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E62" s="15"/>
+      <c r="F62" s="8">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C63" s="3">
-        <v>297817</v>
-      </c>
-      <c r="D63" s="4" t="s">
+      <c r="C63" s="6">
+        <v>100391</v>
+      </c>
+      <c r="D63" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="E63" s="5"/>
-      <c r="F63" s="7">
+      <c r="E63" s="15"/>
+      <c r="F63" s="8">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C64" s="6">
+        <v>113227</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E64" s="15"/>
+      <c r="F64" s="8">
         <v>6.99</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C64" s="3">
+    <row r="65" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C65" s="6">
+        <v>111086</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65" s="15"/>
+      <c r="F65" s="8">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C66" s="6">
+        <v>257710</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E66" s="15"/>
+      <c r="F66" s="8">
+        <v>16.989999999999998</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C67" s="6">
+        <v>261174</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E67" s="15"/>
+      <c r="F67" s="8">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C69" s="6">
         <v>154004</v>
       </c>
-      <c r="D64" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="E64" s="5"/>
-      <c r="F64" s="7">
+      <c r="D69" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E69" s="15"/>
+      <c r="F69" s="8">
         <v>7.99</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C65" s="3">
+    <row r="70" spans="1:6" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C70" s="6">
         <v>117175</v>
       </c>
-      <c r="D65" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="E65" s="5"/>
-      <c r="F65" s="7">
+      <c r="D70" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E70" s="15"/>
+      <c r="F70" s="8">
         <v>5.99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C66" s="3">
-        <v>139778</v>
-      </c>
-      <c r="D66" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E66" s="5"/>
-      <c r="F66" s="7">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C67" s="3">
-        <v>286959</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E67" s="5"/>
-      <c r="F67" s="7">
-        <v>14.39</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C68" s="3">
-        <v>320648</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E68" s="5"/>
-      <c r="F68" s="7">
-        <v>3.39</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C69" s="3">
-        <v>113227</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="E69" s="5"/>
-      <c r="F69" s="7">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C70" s="3">
-        <v>111086</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E70" s="5"/>
-      <c r="F70" s="7">
-        <v>5.49</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="86" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="81" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
-    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS&amp;C&amp;P - &amp;N</oddHeader>
+    <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - QUINTA E SEXTA&amp;C&amp;P - &amp;N&amp;RESSAS OFERTAS DURARÃO APENAS 2 DIAS, QUINTA E SEXTA</oddHeader>
   </headerFooter>
 </worksheet>
 </file>